--- a/Data/IpAddressConditionalFormattingTemplate.xlsx
+++ b/Data/IpAddressConditionalFormattingTemplate.xlsx
@@ -195,7 +195,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="120">
+  <dxfs count="145">
     <dxf>
       <fill>
         <patternFill>
@@ -262,6 +262,181 @@
     <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ffadd8e6"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ff59abf8"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ffffb6c1"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="fffacd90"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="fff2ceef"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ffadd8e6"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ff59abf8"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ffffb6c1"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="fffacd90"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="fff2ceef"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ffadd8e6"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ff59abf8"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ffffb6c1"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="fffacd90"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="fff2ceef"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ffadd8e6"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ff59abf8"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ffffb6c1"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="fffacd90"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="fff2ceef"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ffadd8e6"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ff59abf8"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ffffb6c1"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="fffacd90"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="fff2ceef"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
     <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
       <fill>
         <patternFill>
@@ -1529,31 +1704,31 @@
     <row r="78" ht="15" customHeight="1"/>
   </sheetData>
   <conditionalFormatting sqref="A:A">
-    <cfRule priority="1" type="containsText" operator="containsText" text="microsoft" stopIfTrue="1" dxfId="115">
+    <cfRule priority="1" type="containsText" operator="containsText" text="microsoft" stopIfTrue="1" dxfId="140">
       <formula>NOT(ISERROR(SEARCH("microsoft",A1)))</formula>
     </cfRule>
-    <cfRule priority="2" type="containsText" operator="containsText" text="proofpoint" stopIfTrue="1" dxfId="116">
+    <cfRule priority="2" type="containsText" operator="containsText" text="proofpoint" stopIfTrue="1" dxfId="141">
       <formula>NOT(ISERROR(SEARCH("proofpoint",A1)))</formula>
     </cfRule>
-    <cfRule priority="3" type="containsText" operator="containsText" text=" vpn" stopIfTrue="1" dxfId="117">
+    <cfRule priority="3" type="containsText" operator="containsText" text=" vpn" stopIfTrue="1" dxfId="142">
       <formula>NOT(ISERROR(SEARCH(" vpn",A1)))</formula>
     </cfRule>
-    <cfRule priority="4" type="containsText" operator="containsText" text=" tor" stopIfTrue="1" dxfId="117">
+    <cfRule priority="4" type="containsText" operator="containsText" text=" tor" stopIfTrue="1" dxfId="142">
       <formula>NOT(ISERROR(SEARCH(" tor",A1)))</formula>
     </cfRule>
-    <cfRule priority="5" type="containsText" operator="containsText" text=" proxy" stopIfTrue="1" dxfId="117">
+    <cfRule priority="5" type="containsText" operator="containsText" text=" proxy" stopIfTrue="1" dxfId="142">
       <formula>NOT(ISERROR(SEARCH(" proxy",A1)))</formula>
     </cfRule>
-    <cfRule priority="6" type="containsText" operator="containsText" text=" hosting" stopIfTrue="1" dxfId="118">
+    <cfRule priority="6" type="containsText" operator="containsText" text=" hosting" stopIfTrue="1" dxfId="143">
       <formula>NOT(ISERROR(SEARCH(" hosting",A1)))</formula>
     </cfRule>
-    <cfRule priority="7" type="containsText" operator="containsText" text=" cloud" stopIfTrue="1" dxfId="118">
+    <cfRule priority="7" type="containsText" operator="containsText" text=" cloud" stopIfTrue="1" dxfId="143">
       <formula>NOT(ISERROR(SEARCH(" cloud",A1)))</formula>
     </cfRule>
-    <cfRule priority="8" type="containsText" operator="containsText" text=" datacenter" stopIfTrue="1" dxfId="118">
+    <cfRule priority="8" type="containsText" operator="containsText" text=" datacenter" stopIfTrue="1" dxfId="143">
       <formula>NOT(ISERROR(SEARCH(" datacenter",A1)))</formula>
     </cfRule>
-    <cfRule priority="9" type="containsText" operator="containsText" text="mobile" stopIfTrue="1" dxfId="119">
+    <cfRule priority="9" type="containsText" operator="containsText" text="mobile" stopIfTrue="1" dxfId="144">
       <formula>NOT(ISERROR(SEARCH("mobile",A1)))</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Data/IpAddressConditionalFormattingTemplate.xlsx
+++ b/Data/IpAddressConditionalFormattingTemplate.xlsx
@@ -195,7 +195,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="145">
+  <dxfs count="155">
     <dxf>
       <fill>
         <patternFill>
@@ -262,6 +262,76 @@
     <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ffadd8e6"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ff59abf8"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ffffb6c1"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="fffacd90"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="fff2ceef"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ffadd8e6"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ff59abf8"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ffffb6c1"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="fffacd90"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="fff2ceef"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
     <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
       <fill>
         <patternFill>
@@ -1704,31 +1774,31 @@
     <row r="78" ht="15" customHeight="1"/>
   </sheetData>
   <conditionalFormatting sqref="A:A">
-    <cfRule priority="1" type="containsText" operator="containsText" text="microsoft" stopIfTrue="1" dxfId="140">
+    <cfRule priority="1" type="containsText" operator="containsText" text="microsoft" stopIfTrue="1" dxfId="150">
       <formula>NOT(ISERROR(SEARCH("microsoft",A1)))</formula>
     </cfRule>
-    <cfRule priority="2" type="containsText" operator="containsText" text="proofpoint" stopIfTrue="1" dxfId="141">
+    <cfRule priority="2" type="containsText" operator="containsText" text="proofpoint" stopIfTrue="1" dxfId="151">
       <formula>NOT(ISERROR(SEARCH("proofpoint",A1)))</formula>
     </cfRule>
-    <cfRule priority="3" type="containsText" operator="containsText" text=" vpn" stopIfTrue="1" dxfId="142">
+    <cfRule priority="3" type="containsText" operator="containsText" text=" vpn" stopIfTrue="1" dxfId="152">
       <formula>NOT(ISERROR(SEARCH(" vpn",A1)))</formula>
     </cfRule>
-    <cfRule priority="4" type="containsText" operator="containsText" text=" tor" stopIfTrue="1" dxfId="142">
+    <cfRule priority="4" type="containsText" operator="containsText" text=" tor" stopIfTrue="1" dxfId="152">
       <formula>NOT(ISERROR(SEARCH(" tor",A1)))</formula>
     </cfRule>
-    <cfRule priority="5" type="containsText" operator="containsText" text=" proxy" stopIfTrue="1" dxfId="142">
+    <cfRule priority="5" type="containsText" operator="containsText" text=" proxy" stopIfTrue="1" dxfId="152">
       <formula>NOT(ISERROR(SEARCH(" proxy",A1)))</formula>
     </cfRule>
-    <cfRule priority="6" type="containsText" operator="containsText" text=" hosting" stopIfTrue="1" dxfId="143">
+    <cfRule priority="6" type="containsText" operator="containsText" text=" hosting" stopIfTrue="1" dxfId="153">
       <formula>NOT(ISERROR(SEARCH(" hosting",A1)))</formula>
     </cfRule>
-    <cfRule priority="7" type="containsText" operator="containsText" text=" cloud" stopIfTrue="1" dxfId="143">
+    <cfRule priority="7" type="containsText" operator="containsText" text=" cloud" stopIfTrue="1" dxfId="153">
       <formula>NOT(ISERROR(SEARCH(" cloud",A1)))</formula>
     </cfRule>
-    <cfRule priority="8" type="containsText" operator="containsText" text=" datacenter" stopIfTrue="1" dxfId="143">
+    <cfRule priority="8" type="containsText" operator="containsText" text=" datacenter" stopIfTrue="1" dxfId="153">
       <formula>NOT(ISERROR(SEARCH(" datacenter",A1)))</formula>
     </cfRule>
-    <cfRule priority="9" type="containsText" operator="containsText" text="mobile" stopIfTrue="1" dxfId="144">
+    <cfRule priority="9" type="containsText" operator="containsText" text="mobile" stopIfTrue="1" dxfId="154">
       <formula>NOT(ISERROR(SEARCH("mobile",A1)))</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Data/IpAddressConditionalFormattingTemplate.xlsx
+++ b/Data/IpAddressConditionalFormattingTemplate.xlsx
@@ -195,7 +195,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="155">
+  <dxfs count="180">
     <dxf>
       <fill>
         <patternFill>
@@ -262,6 +262,181 @@
     <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ffadd8e6"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ff59abf8"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ffffb6c1"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="fffacd90"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="fff2ceef"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ffadd8e6"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ff59abf8"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ffffb6c1"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="fffacd90"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="fff2ceef"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ffadd8e6"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ff59abf8"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ffffb6c1"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="fffacd90"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="fff2ceef"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ffadd8e6"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ff59abf8"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ffffb6c1"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="fffacd90"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="fff2ceef"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ffadd8e6"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ff59abf8"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ffffb6c1"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="fffacd90"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="fff2ceef"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
     <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
       <fill>
         <patternFill>
@@ -1774,31 +1949,31 @@
     <row r="78" ht="15" customHeight="1"/>
   </sheetData>
   <conditionalFormatting sqref="A:A">
-    <cfRule priority="1" type="containsText" operator="containsText" text="microsoft" stopIfTrue="1" dxfId="150">
+    <cfRule priority="1" type="containsText" operator="containsText" text="microsoft" stopIfTrue="1" dxfId="175">
       <formula>NOT(ISERROR(SEARCH("microsoft",A1)))</formula>
     </cfRule>
-    <cfRule priority="2" type="containsText" operator="containsText" text="proofpoint" stopIfTrue="1" dxfId="151">
+    <cfRule priority="2" type="containsText" operator="containsText" text="proofpoint" stopIfTrue="1" dxfId="176">
       <formula>NOT(ISERROR(SEARCH("proofpoint",A1)))</formula>
     </cfRule>
-    <cfRule priority="3" type="containsText" operator="containsText" text=" vpn" stopIfTrue="1" dxfId="152">
+    <cfRule priority="3" type="containsText" operator="containsText" text=" vpn" stopIfTrue="1" dxfId="177">
       <formula>NOT(ISERROR(SEARCH(" vpn",A1)))</formula>
     </cfRule>
-    <cfRule priority="4" type="containsText" operator="containsText" text=" tor" stopIfTrue="1" dxfId="152">
+    <cfRule priority="4" type="containsText" operator="containsText" text=" tor" stopIfTrue="1" dxfId="177">
       <formula>NOT(ISERROR(SEARCH(" tor",A1)))</formula>
     </cfRule>
-    <cfRule priority="5" type="containsText" operator="containsText" text=" proxy" stopIfTrue="1" dxfId="152">
+    <cfRule priority="5" type="containsText" operator="containsText" text=" proxy" stopIfTrue="1" dxfId="177">
       <formula>NOT(ISERROR(SEARCH(" proxy",A1)))</formula>
     </cfRule>
-    <cfRule priority="6" type="containsText" operator="containsText" text=" hosting" stopIfTrue="1" dxfId="153">
+    <cfRule priority="6" type="containsText" operator="containsText" text=" hosting" stopIfTrue="1" dxfId="178">
       <formula>NOT(ISERROR(SEARCH(" hosting",A1)))</formula>
     </cfRule>
-    <cfRule priority="7" type="containsText" operator="containsText" text=" cloud" stopIfTrue="1" dxfId="153">
+    <cfRule priority="7" type="containsText" operator="containsText" text=" cloud" stopIfTrue="1" dxfId="178">
       <formula>NOT(ISERROR(SEARCH(" cloud",A1)))</formula>
     </cfRule>
-    <cfRule priority="8" type="containsText" operator="containsText" text=" datacenter" stopIfTrue="1" dxfId="153">
+    <cfRule priority="8" type="containsText" operator="containsText" text=" datacenter" stopIfTrue="1" dxfId="178">
       <formula>NOT(ISERROR(SEARCH(" datacenter",A1)))</formula>
     </cfRule>
-    <cfRule priority="9" type="containsText" operator="containsText" text="mobile" stopIfTrue="1" dxfId="154">
+    <cfRule priority="9" type="containsText" operator="containsText" text="mobile" stopIfTrue="1" dxfId="179">
       <formula>NOT(ISERROR(SEARCH("mobile",A1)))</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Data/IpAddressConditionalFormattingTemplate.xlsx
+++ b/Data/IpAddressConditionalFormattingTemplate.xlsx
@@ -195,7 +195,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="180">
+  <dxfs count="210">
     <dxf>
       <fill>
         <patternFill>
@@ -262,6 +262,216 @@
     <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ffadd8e6"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ff59abf8"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ffffb6c1"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="fffacd90"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="fff2ceef"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ffadd8e6"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ff59abf8"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ffffb6c1"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="fffacd90"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="fff2ceef"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ffadd8e6"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ff59abf8"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ffffb6c1"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="fffacd90"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="fff2ceef"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ffadd8e6"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ff59abf8"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ffffb6c1"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="fffacd90"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="fff2ceef"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ffadd8e6"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ff59abf8"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ffffb6c1"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="fffacd90"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="fff2ceef"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ffadd8e6"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ff59abf8"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ffffb6c1"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="fffacd90"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="fff2ceef"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
     <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
       <fill>
         <patternFill>
@@ -1949,31 +2159,31 @@
     <row r="78" ht="15" customHeight="1"/>
   </sheetData>
   <conditionalFormatting sqref="A:A">
-    <cfRule priority="1" type="containsText" operator="containsText" text="microsoft" stopIfTrue="1" dxfId="175">
+    <cfRule priority="1" type="containsText" operator="containsText" text="microsoft" stopIfTrue="1" dxfId="205">
       <formula>NOT(ISERROR(SEARCH("microsoft",A1)))</formula>
     </cfRule>
-    <cfRule priority="2" type="containsText" operator="containsText" text="proofpoint" stopIfTrue="1" dxfId="176">
+    <cfRule priority="2" type="containsText" operator="containsText" text="proofpoint" stopIfTrue="1" dxfId="206">
       <formula>NOT(ISERROR(SEARCH("proofpoint",A1)))</formula>
     </cfRule>
-    <cfRule priority="3" type="containsText" operator="containsText" text=" vpn" stopIfTrue="1" dxfId="177">
+    <cfRule priority="3" type="containsText" operator="containsText" text=" vpn" stopIfTrue="1" dxfId="207">
       <formula>NOT(ISERROR(SEARCH(" vpn",A1)))</formula>
     </cfRule>
-    <cfRule priority="4" type="containsText" operator="containsText" text=" tor" stopIfTrue="1" dxfId="177">
+    <cfRule priority="4" type="containsText" operator="containsText" text=" tor" stopIfTrue="1" dxfId="207">
       <formula>NOT(ISERROR(SEARCH(" tor",A1)))</formula>
     </cfRule>
-    <cfRule priority="5" type="containsText" operator="containsText" text=" proxy" stopIfTrue="1" dxfId="177">
+    <cfRule priority="5" type="containsText" operator="containsText" text=" proxy" stopIfTrue="1" dxfId="207">
       <formula>NOT(ISERROR(SEARCH(" proxy",A1)))</formula>
     </cfRule>
-    <cfRule priority="6" type="containsText" operator="containsText" text=" hosting" stopIfTrue="1" dxfId="178">
+    <cfRule priority="6" type="containsText" operator="containsText" text=" hosting" stopIfTrue="1" dxfId="208">
       <formula>NOT(ISERROR(SEARCH(" hosting",A1)))</formula>
     </cfRule>
-    <cfRule priority="7" type="containsText" operator="containsText" text=" cloud" stopIfTrue="1" dxfId="178">
+    <cfRule priority="7" type="containsText" operator="containsText" text=" cloud" stopIfTrue="1" dxfId="208">
       <formula>NOT(ISERROR(SEARCH(" cloud",A1)))</formula>
     </cfRule>
-    <cfRule priority="8" type="containsText" operator="containsText" text=" datacenter" stopIfTrue="1" dxfId="178">
+    <cfRule priority="8" type="containsText" operator="containsText" text=" datacenter" stopIfTrue="1" dxfId="208">
       <formula>NOT(ISERROR(SEARCH(" datacenter",A1)))</formula>
     </cfRule>
-    <cfRule priority="9" type="containsText" operator="containsText" text="mobile" stopIfTrue="1" dxfId="179">
+    <cfRule priority="9" type="containsText" operator="containsText" text="mobile" stopIfTrue="1" dxfId="209">
       <formula>NOT(ISERROR(SEARCH("mobile",A1)))</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Data/IpAddressConditionalFormattingTemplate.xlsx
+++ b/Data/IpAddressConditionalFormattingTemplate.xlsx
@@ -195,7 +195,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="210">
+  <dxfs count="225">
     <dxf>
       <fill>
         <patternFill>
@@ -262,6 +262,111 @@
     <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ffadd8e6"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ff59abf8"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ffffb6c1"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="fffacd90"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="fff2ceef"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ffadd8e6"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ff59abf8"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ffffb6c1"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="fffacd90"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="fff2ceef"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ffadd8e6"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ff59abf8"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ffffb6c1"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="fffacd90"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="fff2ceef"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
     <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
       <fill>
         <patternFill>
@@ -2159,31 +2264,31 @@
     <row r="78" ht="15" customHeight="1"/>
   </sheetData>
   <conditionalFormatting sqref="A:A">
-    <cfRule priority="1" type="containsText" operator="containsText" text="microsoft" stopIfTrue="1" dxfId="205">
+    <cfRule priority="1" type="containsText" operator="containsText" text="microsoft" stopIfTrue="1" dxfId="220">
       <formula>NOT(ISERROR(SEARCH("microsoft",A1)))</formula>
     </cfRule>
-    <cfRule priority="2" type="containsText" operator="containsText" text="proofpoint" stopIfTrue="1" dxfId="206">
+    <cfRule priority="2" type="containsText" operator="containsText" text="proofpoint" stopIfTrue="1" dxfId="221">
       <formula>NOT(ISERROR(SEARCH("proofpoint",A1)))</formula>
     </cfRule>
-    <cfRule priority="3" type="containsText" operator="containsText" text=" vpn" stopIfTrue="1" dxfId="207">
+    <cfRule priority="3" type="containsText" operator="containsText" text=" vpn" stopIfTrue="1" dxfId="222">
       <formula>NOT(ISERROR(SEARCH(" vpn",A1)))</formula>
     </cfRule>
-    <cfRule priority="4" type="containsText" operator="containsText" text=" tor" stopIfTrue="1" dxfId="207">
+    <cfRule priority="4" type="containsText" operator="containsText" text=" tor" stopIfTrue="1" dxfId="222">
       <formula>NOT(ISERROR(SEARCH(" tor",A1)))</formula>
     </cfRule>
-    <cfRule priority="5" type="containsText" operator="containsText" text=" proxy" stopIfTrue="1" dxfId="207">
+    <cfRule priority="5" type="containsText" operator="containsText" text=" proxy" stopIfTrue="1" dxfId="222">
       <formula>NOT(ISERROR(SEARCH(" proxy",A1)))</formula>
     </cfRule>
-    <cfRule priority="6" type="containsText" operator="containsText" text=" hosting" stopIfTrue="1" dxfId="208">
+    <cfRule priority="6" type="containsText" operator="containsText" text=" hosting" stopIfTrue="1" dxfId="223">
       <formula>NOT(ISERROR(SEARCH(" hosting",A1)))</formula>
     </cfRule>
-    <cfRule priority="7" type="containsText" operator="containsText" text=" cloud" stopIfTrue="1" dxfId="208">
+    <cfRule priority="7" type="containsText" operator="containsText" text=" cloud" stopIfTrue="1" dxfId="223">
       <formula>NOT(ISERROR(SEARCH(" cloud",A1)))</formula>
     </cfRule>
-    <cfRule priority="8" type="containsText" operator="containsText" text=" datacenter" stopIfTrue="1" dxfId="208">
+    <cfRule priority="8" type="containsText" operator="containsText" text=" datacenter" stopIfTrue="1" dxfId="223">
       <formula>NOT(ISERROR(SEARCH(" datacenter",A1)))</formula>
     </cfRule>
-    <cfRule priority="9" type="containsText" operator="containsText" text="mobile" stopIfTrue="1" dxfId="209">
+    <cfRule priority="9" type="containsText" operator="containsText" text="mobile" stopIfTrue="1" dxfId="224">
       <formula>NOT(ISERROR(SEARCH("mobile",A1)))</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Data/IpAddressConditionalFormattingTemplate.xlsx
+++ b/Data/IpAddressConditionalFormattingTemplate.xlsx
@@ -195,7 +195,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="225">
+  <dxfs count="230">
     <dxf>
       <fill>
         <patternFill>
@@ -262,6 +262,41 @@
     <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ffadd8e6"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ff59abf8"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ffffb6c1"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="fffacd90"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="fff2ceef"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
     <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
       <fill>
         <patternFill>
@@ -2264,31 +2299,31 @@
     <row r="78" ht="15" customHeight="1"/>
   </sheetData>
   <conditionalFormatting sqref="A:A">
-    <cfRule priority="1" type="containsText" operator="containsText" text="microsoft" stopIfTrue="1" dxfId="220">
+    <cfRule priority="1" type="containsText" operator="containsText" text="microsoft" stopIfTrue="1" dxfId="225">
       <formula>NOT(ISERROR(SEARCH("microsoft",A1)))</formula>
     </cfRule>
-    <cfRule priority="2" type="containsText" operator="containsText" text="proofpoint" stopIfTrue="1" dxfId="221">
+    <cfRule priority="2" type="containsText" operator="containsText" text="proofpoint" stopIfTrue="1" dxfId="226">
       <formula>NOT(ISERROR(SEARCH("proofpoint",A1)))</formula>
     </cfRule>
-    <cfRule priority="3" type="containsText" operator="containsText" text=" vpn" stopIfTrue="1" dxfId="222">
+    <cfRule priority="3" type="containsText" operator="containsText" text=" vpn" stopIfTrue="1" dxfId="227">
       <formula>NOT(ISERROR(SEARCH(" vpn",A1)))</formula>
     </cfRule>
-    <cfRule priority="4" type="containsText" operator="containsText" text=" tor" stopIfTrue="1" dxfId="222">
+    <cfRule priority="4" type="containsText" operator="containsText" text=" tor" stopIfTrue="1" dxfId="227">
       <formula>NOT(ISERROR(SEARCH(" tor",A1)))</formula>
     </cfRule>
-    <cfRule priority="5" type="containsText" operator="containsText" text=" proxy" stopIfTrue="1" dxfId="222">
+    <cfRule priority="5" type="containsText" operator="containsText" text=" proxy" stopIfTrue="1" dxfId="227">
       <formula>NOT(ISERROR(SEARCH(" proxy",A1)))</formula>
     </cfRule>
-    <cfRule priority="6" type="containsText" operator="containsText" text=" hosting" stopIfTrue="1" dxfId="223">
+    <cfRule priority="6" type="containsText" operator="containsText" text=" hosting" stopIfTrue="1" dxfId="228">
       <formula>NOT(ISERROR(SEARCH(" hosting",A1)))</formula>
     </cfRule>
-    <cfRule priority="7" type="containsText" operator="containsText" text=" cloud" stopIfTrue="1" dxfId="223">
+    <cfRule priority="7" type="containsText" operator="containsText" text=" cloud" stopIfTrue="1" dxfId="228">
       <formula>NOT(ISERROR(SEARCH(" cloud",A1)))</formula>
     </cfRule>
-    <cfRule priority="8" type="containsText" operator="containsText" text=" datacenter" stopIfTrue="1" dxfId="223">
+    <cfRule priority="8" type="containsText" operator="containsText" text=" datacenter" stopIfTrue="1" dxfId="228">
       <formula>NOT(ISERROR(SEARCH(" datacenter",A1)))</formula>
     </cfRule>
-    <cfRule priority="9" type="containsText" operator="containsText" text="mobile" stopIfTrue="1" dxfId="224">
+    <cfRule priority="9" type="containsText" operator="containsText" text="mobile" stopIfTrue="1" dxfId="229">
       <formula>NOT(ISERROR(SEARCH("mobile",A1)))</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Data/IpAddressConditionalFormattingTemplate.xlsx
+++ b/Data/IpAddressConditionalFormattingTemplate.xlsx
@@ -195,7 +195,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="230">
+  <dxfs count="240">
     <dxf>
       <fill>
         <patternFill>
@@ -262,6 +262,76 @@
     <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ffadd8e6"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ff59abf8"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ffffb6c1"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="fffacd90"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="fff2ceef"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ffadd8e6"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ff59abf8"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ffffb6c1"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="fffacd90"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="fff2ceef"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
     <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
       <fill>
         <patternFill>
@@ -2299,31 +2369,31 @@
     <row r="78" ht="15" customHeight="1"/>
   </sheetData>
   <conditionalFormatting sqref="A:A">
-    <cfRule priority="1" type="containsText" operator="containsText" text="microsoft" stopIfTrue="1" dxfId="225">
+    <cfRule priority="1" type="containsText" operator="containsText" text="microsoft" stopIfTrue="1" dxfId="235">
       <formula>NOT(ISERROR(SEARCH("microsoft",A1)))</formula>
     </cfRule>
-    <cfRule priority="2" type="containsText" operator="containsText" text="proofpoint" stopIfTrue="1" dxfId="226">
+    <cfRule priority="2" type="containsText" operator="containsText" text="proofpoint" stopIfTrue="1" dxfId="236">
       <formula>NOT(ISERROR(SEARCH("proofpoint",A1)))</formula>
     </cfRule>
-    <cfRule priority="3" type="containsText" operator="containsText" text=" vpn" stopIfTrue="1" dxfId="227">
+    <cfRule priority="3" type="containsText" operator="containsText" text=" vpn" stopIfTrue="1" dxfId="237">
       <formula>NOT(ISERROR(SEARCH(" vpn",A1)))</formula>
     </cfRule>
-    <cfRule priority="4" type="containsText" operator="containsText" text=" tor" stopIfTrue="1" dxfId="227">
+    <cfRule priority="4" type="containsText" operator="containsText" text=" tor" stopIfTrue="1" dxfId="237">
       <formula>NOT(ISERROR(SEARCH(" tor",A1)))</formula>
     </cfRule>
-    <cfRule priority="5" type="containsText" operator="containsText" text=" proxy" stopIfTrue="1" dxfId="227">
+    <cfRule priority="5" type="containsText" operator="containsText" text=" proxy" stopIfTrue="1" dxfId="237">
       <formula>NOT(ISERROR(SEARCH(" proxy",A1)))</formula>
     </cfRule>
-    <cfRule priority="6" type="containsText" operator="containsText" text=" hosting" stopIfTrue="1" dxfId="228">
+    <cfRule priority="6" type="containsText" operator="containsText" text=" hosting" stopIfTrue="1" dxfId="238">
       <formula>NOT(ISERROR(SEARCH(" hosting",A1)))</formula>
     </cfRule>
-    <cfRule priority="7" type="containsText" operator="containsText" text=" cloud" stopIfTrue="1" dxfId="228">
+    <cfRule priority="7" type="containsText" operator="containsText" text=" cloud" stopIfTrue="1" dxfId="238">
       <formula>NOT(ISERROR(SEARCH(" cloud",A1)))</formula>
     </cfRule>
-    <cfRule priority="8" type="containsText" operator="containsText" text=" datacenter" stopIfTrue="1" dxfId="228">
+    <cfRule priority="8" type="containsText" operator="containsText" text=" datacenter" stopIfTrue="1" dxfId="238">
       <formula>NOT(ISERROR(SEARCH(" datacenter",A1)))</formula>
     </cfRule>
-    <cfRule priority="9" type="containsText" operator="containsText" text="mobile" stopIfTrue="1" dxfId="229">
+    <cfRule priority="9" type="containsText" operator="containsText" text="mobile" stopIfTrue="1" dxfId="239">
       <formula>NOT(ISERROR(SEARCH("mobile",A1)))</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Data/IpAddressConditionalFormattingTemplate.xlsx
+++ b/Data/IpAddressConditionalFormattingTemplate.xlsx
@@ -195,7 +195,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="240">
+  <dxfs count="285">
     <dxf>
       <fill>
         <patternFill>
@@ -262,6 +262,321 @@
     <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ffadd8e6"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ff59abf8"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ffffb6c1"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="fffacd90"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="fff2ceef"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ffadd8e6"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ff59abf8"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ffffb6c1"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="fffacd90"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="fff2ceef"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ffadd8e6"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ff59abf8"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ffffb6c1"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="fffacd90"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="fff2ceef"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ffadd8e6"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ff59abf8"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ffffb6c1"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="fffacd90"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="fff2ceef"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ffadd8e6"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ff59abf8"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ffffb6c1"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="fffacd90"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="fff2ceef"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ffadd8e6"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ff59abf8"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ffffb6c1"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="fffacd90"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="fff2ceef"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ffadd8e6"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ff59abf8"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ffffb6c1"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="fffacd90"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="fff2ceef"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ffadd8e6"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ff59abf8"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ffffb6c1"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="fffacd90"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="fff2ceef"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ffadd8e6"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ff59abf8"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ffffb6c1"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="fffacd90"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="fff2ceef"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
     <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
       <fill>
         <patternFill>
@@ -2369,31 +2684,31 @@
     <row r="78" ht="15" customHeight="1"/>
   </sheetData>
   <conditionalFormatting sqref="A:A">
-    <cfRule priority="1" type="containsText" operator="containsText" text="microsoft" stopIfTrue="1" dxfId="235">
+    <cfRule priority="1" type="containsText" operator="containsText" text="microsoft" stopIfTrue="1" dxfId="280">
       <formula>NOT(ISERROR(SEARCH("microsoft",A1)))</formula>
     </cfRule>
-    <cfRule priority="2" type="containsText" operator="containsText" text="proofpoint" stopIfTrue="1" dxfId="236">
+    <cfRule priority="2" type="containsText" operator="containsText" text="proofpoint" stopIfTrue="1" dxfId="281">
       <formula>NOT(ISERROR(SEARCH("proofpoint",A1)))</formula>
     </cfRule>
-    <cfRule priority="3" type="containsText" operator="containsText" text=" vpn" stopIfTrue="1" dxfId="237">
+    <cfRule priority="3" type="containsText" operator="containsText" text=" vpn" stopIfTrue="1" dxfId="282">
       <formula>NOT(ISERROR(SEARCH(" vpn",A1)))</formula>
     </cfRule>
-    <cfRule priority="4" type="containsText" operator="containsText" text=" tor" stopIfTrue="1" dxfId="237">
+    <cfRule priority="4" type="containsText" operator="containsText" text=" tor" stopIfTrue="1" dxfId="282">
       <formula>NOT(ISERROR(SEARCH(" tor",A1)))</formula>
     </cfRule>
-    <cfRule priority="5" type="containsText" operator="containsText" text=" proxy" stopIfTrue="1" dxfId="237">
+    <cfRule priority="5" type="containsText" operator="containsText" text=" proxy" stopIfTrue="1" dxfId="282">
       <formula>NOT(ISERROR(SEARCH(" proxy",A1)))</formula>
     </cfRule>
-    <cfRule priority="6" type="containsText" operator="containsText" text=" hosting" stopIfTrue="1" dxfId="238">
+    <cfRule priority="6" type="containsText" operator="containsText" text=" hosting" stopIfTrue="1" dxfId="283">
       <formula>NOT(ISERROR(SEARCH(" hosting",A1)))</formula>
     </cfRule>
-    <cfRule priority="7" type="containsText" operator="containsText" text=" cloud" stopIfTrue="1" dxfId="238">
+    <cfRule priority="7" type="containsText" operator="containsText" text=" cloud" stopIfTrue="1" dxfId="283">
       <formula>NOT(ISERROR(SEARCH(" cloud",A1)))</formula>
     </cfRule>
-    <cfRule priority="8" type="containsText" operator="containsText" text=" datacenter" stopIfTrue="1" dxfId="238">
+    <cfRule priority="8" type="containsText" operator="containsText" text=" datacenter" stopIfTrue="1" dxfId="283">
       <formula>NOT(ISERROR(SEARCH(" datacenter",A1)))</formula>
     </cfRule>
-    <cfRule priority="9" type="containsText" operator="containsText" text="mobile" stopIfTrue="1" dxfId="239">
+    <cfRule priority="9" type="containsText" operator="containsText" text="mobile" stopIfTrue="1" dxfId="284">
       <formula>NOT(ISERROR(SEARCH("mobile",A1)))</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Data/IpAddressConditionalFormattingTemplate.xlsx
+++ b/Data/IpAddressConditionalFormattingTemplate.xlsx
@@ -195,7 +195,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="285">
+  <dxfs count="295">
     <dxf>
       <fill>
         <patternFill>
@@ -262,6 +262,76 @@
     <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ffadd8e6"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ff59abf8"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ffffb6c1"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="fffacd90"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="fff2ceef"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ffadd8e6"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ff59abf8"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ffffb6c1"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="fffacd90"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="fff2ceef"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
     <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
       <fill>
         <patternFill>
@@ -2684,31 +2754,31 @@
     <row r="78" ht="15" customHeight="1"/>
   </sheetData>
   <conditionalFormatting sqref="A:A">
-    <cfRule priority="1" type="containsText" operator="containsText" text="microsoft" stopIfTrue="1" dxfId="280">
+    <cfRule priority="1" type="containsText" operator="containsText" text="microsoft" stopIfTrue="1" dxfId="290">
       <formula>NOT(ISERROR(SEARCH("microsoft",A1)))</formula>
     </cfRule>
-    <cfRule priority="2" type="containsText" operator="containsText" text="proofpoint" stopIfTrue="1" dxfId="281">
+    <cfRule priority="2" type="containsText" operator="containsText" text="proofpoint" stopIfTrue="1" dxfId="291">
       <formula>NOT(ISERROR(SEARCH("proofpoint",A1)))</formula>
     </cfRule>
-    <cfRule priority="3" type="containsText" operator="containsText" text=" vpn" stopIfTrue="1" dxfId="282">
+    <cfRule priority="3" type="containsText" operator="containsText" text=" vpn" stopIfTrue="1" dxfId="292">
       <formula>NOT(ISERROR(SEARCH(" vpn",A1)))</formula>
     </cfRule>
-    <cfRule priority="4" type="containsText" operator="containsText" text=" tor" stopIfTrue="1" dxfId="282">
+    <cfRule priority="4" type="containsText" operator="containsText" text=" tor" stopIfTrue="1" dxfId="292">
       <formula>NOT(ISERROR(SEARCH(" tor",A1)))</formula>
     </cfRule>
-    <cfRule priority="5" type="containsText" operator="containsText" text=" proxy" stopIfTrue="1" dxfId="282">
+    <cfRule priority="5" type="containsText" operator="containsText" text=" proxy" stopIfTrue="1" dxfId="292">
       <formula>NOT(ISERROR(SEARCH(" proxy",A1)))</formula>
     </cfRule>
-    <cfRule priority="6" type="containsText" operator="containsText" text=" hosting" stopIfTrue="1" dxfId="283">
+    <cfRule priority="6" type="containsText" operator="containsText" text=" hosting" stopIfTrue="1" dxfId="293">
       <formula>NOT(ISERROR(SEARCH(" hosting",A1)))</formula>
     </cfRule>
-    <cfRule priority="7" type="containsText" operator="containsText" text=" cloud" stopIfTrue="1" dxfId="283">
+    <cfRule priority="7" type="containsText" operator="containsText" text=" cloud" stopIfTrue="1" dxfId="293">
       <formula>NOT(ISERROR(SEARCH(" cloud",A1)))</formula>
     </cfRule>
-    <cfRule priority="8" type="containsText" operator="containsText" text=" datacenter" stopIfTrue="1" dxfId="283">
+    <cfRule priority="8" type="containsText" operator="containsText" text=" datacenter" stopIfTrue="1" dxfId="293">
       <formula>NOT(ISERROR(SEARCH(" datacenter",A1)))</formula>
     </cfRule>
-    <cfRule priority="9" type="containsText" operator="containsText" text="mobile" stopIfTrue="1" dxfId="284">
+    <cfRule priority="9" type="containsText" operator="containsText" text="mobile" stopIfTrue="1" dxfId="294">
       <formula>NOT(ISERROR(SEARCH("mobile",A1)))</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Data/IpAddressConditionalFormattingTemplate.xlsx
+++ b/Data/IpAddressConditionalFormattingTemplate.xlsx
@@ -195,7 +195,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="295">
+  <dxfs count="300">
     <dxf>
       <fill>
         <patternFill>
@@ -262,6 +262,41 @@
     <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ffadd8e6"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ff59abf8"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ffffb6c1"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="fffacd90"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="fff2ceef"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
     <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
       <fill>
         <patternFill>
@@ -2754,31 +2789,31 @@
     <row r="78" ht="15" customHeight="1"/>
   </sheetData>
   <conditionalFormatting sqref="A:A">
-    <cfRule priority="1" type="containsText" operator="containsText" text="microsoft" stopIfTrue="1" dxfId="290">
+    <cfRule priority="1" type="containsText" operator="containsText" text="microsoft" stopIfTrue="1" dxfId="295">
       <formula>NOT(ISERROR(SEARCH("microsoft",A1)))</formula>
     </cfRule>
-    <cfRule priority="2" type="containsText" operator="containsText" text="proofpoint" stopIfTrue="1" dxfId="291">
+    <cfRule priority="2" type="containsText" operator="containsText" text="proofpoint" stopIfTrue="1" dxfId="296">
       <formula>NOT(ISERROR(SEARCH("proofpoint",A1)))</formula>
     </cfRule>
-    <cfRule priority="3" type="containsText" operator="containsText" text=" vpn" stopIfTrue="1" dxfId="292">
+    <cfRule priority="3" type="containsText" operator="containsText" text=" vpn" stopIfTrue="1" dxfId="297">
       <formula>NOT(ISERROR(SEARCH(" vpn",A1)))</formula>
     </cfRule>
-    <cfRule priority="4" type="containsText" operator="containsText" text=" tor" stopIfTrue="1" dxfId="292">
+    <cfRule priority="4" type="containsText" operator="containsText" text=" tor" stopIfTrue="1" dxfId="297">
       <formula>NOT(ISERROR(SEARCH(" tor",A1)))</formula>
     </cfRule>
-    <cfRule priority="5" type="containsText" operator="containsText" text=" proxy" stopIfTrue="1" dxfId="292">
+    <cfRule priority="5" type="containsText" operator="containsText" text=" proxy" stopIfTrue="1" dxfId="297">
       <formula>NOT(ISERROR(SEARCH(" proxy",A1)))</formula>
     </cfRule>
-    <cfRule priority="6" type="containsText" operator="containsText" text=" hosting" stopIfTrue="1" dxfId="293">
+    <cfRule priority="6" type="containsText" operator="containsText" text=" hosting" stopIfTrue="1" dxfId="298">
       <formula>NOT(ISERROR(SEARCH(" hosting",A1)))</formula>
     </cfRule>
-    <cfRule priority="7" type="containsText" operator="containsText" text=" cloud" stopIfTrue="1" dxfId="293">
+    <cfRule priority="7" type="containsText" operator="containsText" text=" cloud" stopIfTrue="1" dxfId="298">
       <formula>NOT(ISERROR(SEARCH(" cloud",A1)))</formula>
     </cfRule>
-    <cfRule priority="8" type="containsText" operator="containsText" text=" datacenter" stopIfTrue="1" dxfId="293">
+    <cfRule priority="8" type="containsText" operator="containsText" text=" datacenter" stopIfTrue="1" dxfId="298">
       <formula>NOT(ISERROR(SEARCH(" datacenter",A1)))</formula>
     </cfRule>
-    <cfRule priority="9" type="containsText" operator="containsText" text="mobile" stopIfTrue="1" dxfId="294">
+    <cfRule priority="9" type="containsText" operator="containsText" text="mobile" stopIfTrue="1" dxfId="299">
       <formula>NOT(ISERROR(SEARCH("mobile",A1)))</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Data/IpAddressConditionalFormattingTemplate.xlsx
+++ b/Data/IpAddressConditionalFormattingTemplate.xlsx
@@ -195,7 +195,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="300">
+  <dxfs count="310">
     <dxf>
       <fill>
         <patternFill>
@@ -262,6 +262,76 @@
     <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ffadd8e6"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ff59abf8"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ffffb6c1"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="fffacd90"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="fff2ceef"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ffadd8e6"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ff59abf8"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ffffb6c1"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="fffacd90"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="fff2ceef"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
     <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
       <fill>
         <patternFill>
@@ -2789,31 +2859,31 @@
     <row r="78" ht="15" customHeight="1"/>
   </sheetData>
   <conditionalFormatting sqref="A:A">
-    <cfRule priority="1" type="containsText" operator="containsText" text="microsoft" stopIfTrue="1" dxfId="295">
+    <cfRule priority="1" type="containsText" operator="containsText" text="microsoft" stopIfTrue="1" dxfId="305">
       <formula>NOT(ISERROR(SEARCH("microsoft",A1)))</formula>
     </cfRule>
-    <cfRule priority="2" type="containsText" operator="containsText" text="proofpoint" stopIfTrue="1" dxfId="296">
+    <cfRule priority="2" type="containsText" operator="containsText" text="proofpoint" stopIfTrue="1" dxfId="306">
       <formula>NOT(ISERROR(SEARCH("proofpoint",A1)))</formula>
     </cfRule>
-    <cfRule priority="3" type="containsText" operator="containsText" text=" vpn" stopIfTrue="1" dxfId="297">
+    <cfRule priority="3" type="containsText" operator="containsText" text=" vpn" stopIfTrue="1" dxfId="307">
       <formula>NOT(ISERROR(SEARCH(" vpn",A1)))</formula>
     </cfRule>
-    <cfRule priority="4" type="containsText" operator="containsText" text=" tor" stopIfTrue="1" dxfId="297">
+    <cfRule priority="4" type="containsText" operator="containsText" text=" tor" stopIfTrue="1" dxfId="307">
       <formula>NOT(ISERROR(SEARCH(" tor",A1)))</formula>
     </cfRule>
-    <cfRule priority="5" type="containsText" operator="containsText" text=" proxy" stopIfTrue="1" dxfId="297">
+    <cfRule priority="5" type="containsText" operator="containsText" text=" proxy" stopIfTrue="1" dxfId="307">
       <formula>NOT(ISERROR(SEARCH(" proxy",A1)))</formula>
     </cfRule>
-    <cfRule priority="6" type="containsText" operator="containsText" text=" hosting" stopIfTrue="1" dxfId="298">
+    <cfRule priority="6" type="containsText" operator="containsText" text=" hosting" stopIfTrue="1" dxfId="308">
       <formula>NOT(ISERROR(SEARCH(" hosting",A1)))</formula>
     </cfRule>
-    <cfRule priority="7" type="containsText" operator="containsText" text=" cloud" stopIfTrue="1" dxfId="298">
+    <cfRule priority="7" type="containsText" operator="containsText" text=" cloud" stopIfTrue="1" dxfId="308">
       <formula>NOT(ISERROR(SEARCH(" cloud",A1)))</formula>
     </cfRule>
-    <cfRule priority="8" type="containsText" operator="containsText" text=" datacenter" stopIfTrue="1" dxfId="298">
+    <cfRule priority="8" type="containsText" operator="containsText" text=" datacenter" stopIfTrue="1" dxfId="308">
       <formula>NOT(ISERROR(SEARCH(" datacenter",A1)))</formula>
     </cfRule>
-    <cfRule priority="9" type="containsText" operator="containsText" text="mobile" stopIfTrue="1" dxfId="299">
+    <cfRule priority="9" type="containsText" operator="containsText" text="mobile" stopIfTrue="1" dxfId="309">
       <formula>NOT(ISERROR(SEARCH("mobile",A1)))</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Data/IpAddressConditionalFormattingTemplate.xlsx
+++ b/Data/IpAddressConditionalFormattingTemplate.xlsx
@@ -195,7 +195,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="310">
+  <dxfs count="325">
     <dxf>
       <fill>
         <patternFill>
@@ -262,6 +262,111 @@
     <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ffadd8e6"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ff59abf8"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ffffb6c1"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="fffacd90"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="fff2ceef"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ffadd8e6"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ff59abf8"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ffffb6c1"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="fffacd90"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="fff2ceef"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ffadd8e6"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ff59abf8"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ffffb6c1"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="fffacd90"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="fff2ceef"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
     <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
       <fill>
         <patternFill>
@@ -2859,31 +2964,31 @@
     <row r="78" ht="15" customHeight="1"/>
   </sheetData>
   <conditionalFormatting sqref="A:A">
-    <cfRule priority="1" type="containsText" operator="containsText" text="microsoft" stopIfTrue="1" dxfId="305">
+    <cfRule priority="1" type="containsText" operator="containsText" text="microsoft" stopIfTrue="1" dxfId="320">
       <formula>NOT(ISERROR(SEARCH("microsoft",A1)))</formula>
     </cfRule>
-    <cfRule priority="2" type="containsText" operator="containsText" text="proofpoint" stopIfTrue="1" dxfId="306">
+    <cfRule priority="2" type="containsText" operator="containsText" text="proofpoint" stopIfTrue="1" dxfId="321">
       <formula>NOT(ISERROR(SEARCH("proofpoint",A1)))</formula>
     </cfRule>
-    <cfRule priority="3" type="containsText" operator="containsText" text=" vpn" stopIfTrue="1" dxfId="307">
+    <cfRule priority="3" type="containsText" operator="containsText" text=" vpn" stopIfTrue="1" dxfId="322">
       <formula>NOT(ISERROR(SEARCH(" vpn",A1)))</formula>
     </cfRule>
-    <cfRule priority="4" type="containsText" operator="containsText" text=" tor" stopIfTrue="1" dxfId="307">
+    <cfRule priority="4" type="containsText" operator="containsText" text=" tor" stopIfTrue="1" dxfId="322">
       <formula>NOT(ISERROR(SEARCH(" tor",A1)))</formula>
     </cfRule>
-    <cfRule priority="5" type="containsText" operator="containsText" text=" proxy" stopIfTrue="1" dxfId="307">
+    <cfRule priority="5" type="containsText" operator="containsText" text=" proxy" stopIfTrue="1" dxfId="322">
       <formula>NOT(ISERROR(SEARCH(" proxy",A1)))</formula>
     </cfRule>
-    <cfRule priority="6" type="containsText" operator="containsText" text=" hosting" stopIfTrue="1" dxfId="308">
+    <cfRule priority="6" type="containsText" operator="containsText" text=" hosting" stopIfTrue="1" dxfId="323">
       <formula>NOT(ISERROR(SEARCH(" hosting",A1)))</formula>
     </cfRule>
-    <cfRule priority="7" type="containsText" operator="containsText" text=" cloud" stopIfTrue="1" dxfId="308">
+    <cfRule priority="7" type="containsText" operator="containsText" text=" cloud" stopIfTrue="1" dxfId="323">
       <formula>NOT(ISERROR(SEARCH(" cloud",A1)))</formula>
     </cfRule>
-    <cfRule priority="8" type="containsText" operator="containsText" text=" datacenter" stopIfTrue="1" dxfId="308">
+    <cfRule priority="8" type="containsText" operator="containsText" text=" datacenter" stopIfTrue="1" dxfId="323">
       <formula>NOT(ISERROR(SEARCH(" datacenter",A1)))</formula>
     </cfRule>
-    <cfRule priority="9" type="containsText" operator="containsText" text="mobile" stopIfTrue="1" dxfId="309">
+    <cfRule priority="9" type="containsText" operator="containsText" text="mobile" stopIfTrue="1" dxfId="324">
       <formula>NOT(ISERROR(SEARCH("mobile",A1)))</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Data/IpAddressConditionalFormattingTemplate.xlsx
+++ b/Data/IpAddressConditionalFormattingTemplate.xlsx
@@ -195,7 +195,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="310">
+  <dxfs count="330">
     <dxf>
       <fill>
         <patternFill>
@@ -262,6 +262,146 @@
     <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ffadd8e6"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ff59abf8"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ffffb6c1"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="fffacd90"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="fff2ceef"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ffadd8e6"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ff59abf8"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ffffb6c1"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="fffacd90"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="fff2ceef"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ffadd8e6"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ff59abf8"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ffffb6c1"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="fffacd90"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="fff2ceef"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ffadd8e6"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ff59abf8"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ffffb6c1"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="fffacd90"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="fff2ceef"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
     <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
       <fill>
         <patternFill>
@@ -2859,31 +2999,31 @@
     <row r="78" ht="15" customHeight="1"/>
   </sheetData>
   <conditionalFormatting sqref="A:A">
-    <cfRule priority="1" type="containsText" operator="containsText" text="microsoft" stopIfTrue="1" dxfId="305">
+    <cfRule priority="1" type="containsText" operator="containsText" text="microsoft" stopIfTrue="1" dxfId="325">
       <formula>NOT(ISERROR(SEARCH("microsoft",A1)))</formula>
     </cfRule>
-    <cfRule priority="2" type="containsText" operator="containsText" text="proofpoint" stopIfTrue="1" dxfId="306">
+    <cfRule priority="2" type="containsText" operator="containsText" text="proofpoint" stopIfTrue="1" dxfId="326">
       <formula>NOT(ISERROR(SEARCH("proofpoint",A1)))</formula>
     </cfRule>
-    <cfRule priority="3" type="containsText" operator="containsText" text=" vpn" stopIfTrue="1" dxfId="307">
+    <cfRule priority="3" type="containsText" operator="containsText" text=" vpn" stopIfTrue="1" dxfId="327">
       <formula>NOT(ISERROR(SEARCH(" vpn",A1)))</formula>
     </cfRule>
-    <cfRule priority="4" type="containsText" operator="containsText" text=" tor" stopIfTrue="1" dxfId="307">
+    <cfRule priority="4" type="containsText" operator="containsText" text=" tor" stopIfTrue="1" dxfId="327">
       <formula>NOT(ISERROR(SEARCH(" tor",A1)))</formula>
     </cfRule>
-    <cfRule priority="5" type="containsText" operator="containsText" text=" proxy" stopIfTrue="1" dxfId="307">
+    <cfRule priority="5" type="containsText" operator="containsText" text=" proxy" stopIfTrue="1" dxfId="327">
       <formula>NOT(ISERROR(SEARCH(" proxy",A1)))</formula>
     </cfRule>
-    <cfRule priority="6" type="containsText" operator="containsText" text=" hosting" stopIfTrue="1" dxfId="308">
+    <cfRule priority="6" type="containsText" operator="containsText" text=" hosting" stopIfTrue="1" dxfId="328">
       <formula>NOT(ISERROR(SEARCH(" hosting",A1)))</formula>
     </cfRule>
-    <cfRule priority="7" type="containsText" operator="containsText" text=" cloud" stopIfTrue="1" dxfId="308">
+    <cfRule priority="7" type="containsText" operator="containsText" text=" cloud" stopIfTrue="1" dxfId="328">
       <formula>NOT(ISERROR(SEARCH(" cloud",A1)))</formula>
     </cfRule>
-    <cfRule priority="8" type="containsText" operator="containsText" text=" datacenter" stopIfTrue="1" dxfId="308">
+    <cfRule priority="8" type="containsText" operator="containsText" text=" datacenter" stopIfTrue="1" dxfId="328">
       <formula>NOT(ISERROR(SEARCH(" datacenter",A1)))</formula>
     </cfRule>
-    <cfRule priority="9" type="containsText" operator="containsText" text="mobile" stopIfTrue="1" dxfId="309">
+    <cfRule priority="9" type="containsText" operator="containsText" text="mobile" stopIfTrue="1" dxfId="329">
       <formula>NOT(ISERROR(SEARCH("mobile",A1)))</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Data/IpAddressConditionalFormattingTemplate.xlsx
+++ b/Data/IpAddressConditionalFormattingTemplate.xlsx
@@ -195,7 +195,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="330">
+  <dxfs count="350">
     <dxf>
       <fill>
         <patternFill>
@@ -262,6 +262,146 @@
     <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ffadd8e6"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ff59abf8"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ffffb6c1"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="fffacd90"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="fff2ceef"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ffadd8e6"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ff59abf8"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ffffb6c1"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="fffacd90"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="fff2ceef"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ffadd8e6"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ff59abf8"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ffffb6c1"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="fffacd90"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="fff2ceef"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ffadd8e6"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ff59abf8"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ffffb6c1"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="fffacd90"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="fff2ceef"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
     <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
       <fill>
         <patternFill>
@@ -2999,31 +3139,31 @@
     <row r="78" ht="15" customHeight="1"/>
   </sheetData>
   <conditionalFormatting sqref="A:A">
-    <cfRule priority="1" type="containsText" operator="containsText" text="microsoft" stopIfTrue="1" dxfId="325">
+    <cfRule priority="1" type="containsText" operator="containsText" text="microsoft" stopIfTrue="1" dxfId="345">
       <formula>NOT(ISERROR(SEARCH("microsoft",A1)))</formula>
     </cfRule>
-    <cfRule priority="2" type="containsText" operator="containsText" text="proofpoint" stopIfTrue="1" dxfId="326">
+    <cfRule priority="2" type="containsText" operator="containsText" text="proofpoint" stopIfTrue="1" dxfId="346">
       <formula>NOT(ISERROR(SEARCH("proofpoint",A1)))</formula>
     </cfRule>
-    <cfRule priority="3" type="containsText" operator="containsText" text=" vpn" stopIfTrue="1" dxfId="327">
+    <cfRule priority="3" type="containsText" operator="containsText" text=" vpn" stopIfTrue="1" dxfId="347">
       <formula>NOT(ISERROR(SEARCH(" vpn",A1)))</formula>
     </cfRule>
-    <cfRule priority="4" type="containsText" operator="containsText" text=" tor" stopIfTrue="1" dxfId="327">
+    <cfRule priority="4" type="containsText" operator="containsText" text=" tor" stopIfTrue="1" dxfId="347">
       <formula>NOT(ISERROR(SEARCH(" tor",A1)))</formula>
     </cfRule>
-    <cfRule priority="5" type="containsText" operator="containsText" text=" proxy" stopIfTrue="1" dxfId="327">
+    <cfRule priority="5" type="containsText" operator="containsText" text=" proxy" stopIfTrue="1" dxfId="347">
       <formula>NOT(ISERROR(SEARCH(" proxy",A1)))</formula>
     </cfRule>
-    <cfRule priority="6" type="containsText" operator="containsText" text=" hosting" stopIfTrue="1" dxfId="328">
+    <cfRule priority="6" type="containsText" operator="containsText" text=" hosting" stopIfTrue="1" dxfId="348">
       <formula>NOT(ISERROR(SEARCH(" hosting",A1)))</formula>
     </cfRule>
-    <cfRule priority="7" type="containsText" operator="containsText" text=" cloud" stopIfTrue="1" dxfId="328">
+    <cfRule priority="7" type="containsText" operator="containsText" text=" cloud" stopIfTrue="1" dxfId="348">
       <formula>NOT(ISERROR(SEARCH(" cloud",A1)))</formula>
     </cfRule>
-    <cfRule priority="8" type="containsText" operator="containsText" text=" datacenter" stopIfTrue="1" dxfId="328">
+    <cfRule priority="8" type="containsText" operator="containsText" text=" datacenter" stopIfTrue="1" dxfId="348">
       <formula>NOT(ISERROR(SEARCH(" datacenter",A1)))</formula>
     </cfRule>
-    <cfRule priority="9" type="containsText" operator="containsText" text="mobile" stopIfTrue="1" dxfId="329">
+    <cfRule priority="9" type="containsText" operator="containsText" text="mobile" stopIfTrue="1" dxfId="349">
       <formula>NOT(ISERROR(SEARCH("mobile",A1)))</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Data/IpAddressConditionalFormattingTemplate.xlsx
+++ b/Data/IpAddressConditionalFormattingTemplate.xlsx
@@ -195,7 +195,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="325">
+  <dxfs count="350">
     <dxf>
       <fill>
         <patternFill>
@@ -262,6 +262,181 @@
     <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ffadd8e6"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ff59abf8"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ffffb6c1"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="fffacd90"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="fff2ceef"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ffadd8e6"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ff59abf8"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ffffb6c1"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="fffacd90"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="fff2ceef"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ffadd8e6"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ff59abf8"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ffffb6c1"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="fffacd90"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="fff2ceef"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ffadd8e6"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ff59abf8"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ffffb6c1"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="fffacd90"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="fff2ceef"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ffadd8e6"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ff59abf8"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ffffb6c1"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="fffacd90"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="fff2ceef"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
     <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
       <fill>
         <patternFill>
@@ -2964,31 +3139,31 @@
     <row r="78" ht="15" customHeight="1"/>
   </sheetData>
   <conditionalFormatting sqref="A:A">
-    <cfRule priority="1" type="containsText" operator="containsText" text="microsoft" stopIfTrue="1" dxfId="320">
+    <cfRule priority="1" type="containsText" operator="containsText" text="microsoft" stopIfTrue="1" dxfId="345">
       <formula>NOT(ISERROR(SEARCH("microsoft",A1)))</formula>
     </cfRule>
-    <cfRule priority="2" type="containsText" operator="containsText" text="proofpoint" stopIfTrue="1" dxfId="321">
+    <cfRule priority="2" type="containsText" operator="containsText" text="proofpoint" stopIfTrue="1" dxfId="346">
       <formula>NOT(ISERROR(SEARCH("proofpoint",A1)))</formula>
     </cfRule>
-    <cfRule priority="3" type="containsText" operator="containsText" text=" vpn" stopIfTrue="1" dxfId="322">
+    <cfRule priority="3" type="containsText" operator="containsText" text=" vpn" stopIfTrue="1" dxfId="347">
       <formula>NOT(ISERROR(SEARCH(" vpn",A1)))</formula>
     </cfRule>
-    <cfRule priority="4" type="containsText" operator="containsText" text=" tor" stopIfTrue="1" dxfId="322">
+    <cfRule priority="4" type="containsText" operator="containsText" text=" tor" stopIfTrue="1" dxfId="347">
       <formula>NOT(ISERROR(SEARCH(" tor",A1)))</formula>
     </cfRule>
-    <cfRule priority="5" type="containsText" operator="containsText" text=" proxy" stopIfTrue="1" dxfId="322">
+    <cfRule priority="5" type="containsText" operator="containsText" text=" proxy" stopIfTrue="1" dxfId="347">
       <formula>NOT(ISERROR(SEARCH(" proxy",A1)))</formula>
     </cfRule>
-    <cfRule priority="6" type="containsText" operator="containsText" text=" hosting" stopIfTrue="1" dxfId="323">
+    <cfRule priority="6" type="containsText" operator="containsText" text=" hosting" stopIfTrue="1" dxfId="348">
       <formula>NOT(ISERROR(SEARCH(" hosting",A1)))</formula>
     </cfRule>
-    <cfRule priority="7" type="containsText" operator="containsText" text=" cloud" stopIfTrue="1" dxfId="323">
+    <cfRule priority="7" type="containsText" operator="containsText" text=" cloud" stopIfTrue="1" dxfId="348">
       <formula>NOT(ISERROR(SEARCH(" cloud",A1)))</formula>
     </cfRule>
-    <cfRule priority="8" type="containsText" operator="containsText" text=" datacenter" stopIfTrue="1" dxfId="323">
+    <cfRule priority="8" type="containsText" operator="containsText" text=" datacenter" stopIfTrue="1" dxfId="348">
       <formula>NOT(ISERROR(SEARCH(" datacenter",A1)))</formula>
     </cfRule>
-    <cfRule priority="9" type="containsText" operator="containsText" text="mobile" stopIfTrue="1" dxfId="324">
+    <cfRule priority="9" type="containsText" operator="containsText" text="mobile" stopIfTrue="1" dxfId="349">
       <formula>NOT(ISERROR(SEARCH("mobile",A1)))</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Data/IpAddressConditionalFormattingTemplate.xlsx
+++ b/Data/IpAddressConditionalFormattingTemplate.xlsx
@@ -195,7 +195,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="350">
+  <dxfs count="360">
     <dxf>
       <fill>
         <patternFill>
@@ -262,6 +262,76 @@
     <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ffadd8e6"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ff59abf8"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ffffb6c1"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="fffacd90"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="fff2ceef"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ffadd8e6"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ff59abf8"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ffffb6c1"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="fffacd90"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="fff2ceef"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
     <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
       <fill>
         <patternFill>
@@ -3139,31 +3209,31 @@
     <row r="78" ht="15" customHeight="1"/>
   </sheetData>
   <conditionalFormatting sqref="A:A">
-    <cfRule priority="1" type="containsText" operator="containsText" text="microsoft" stopIfTrue="1" dxfId="345">
+    <cfRule priority="1" type="containsText" operator="containsText" text="microsoft" stopIfTrue="1" dxfId="355">
       <formula>NOT(ISERROR(SEARCH("microsoft",A1)))</formula>
     </cfRule>
-    <cfRule priority="2" type="containsText" operator="containsText" text="proofpoint" stopIfTrue="1" dxfId="346">
+    <cfRule priority="2" type="containsText" operator="containsText" text="proofpoint" stopIfTrue="1" dxfId="356">
       <formula>NOT(ISERROR(SEARCH("proofpoint",A1)))</formula>
     </cfRule>
-    <cfRule priority="3" type="containsText" operator="containsText" text=" vpn" stopIfTrue="1" dxfId="347">
+    <cfRule priority="3" type="containsText" operator="containsText" text=" vpn" stopIfTrue="1" dxfId="357">
       <formula>NOT(ISERROR(SEARCH(" vpn",A1)))</formula>
     </cfRule>
-    <cfRule priority="4" type="containsText" operator="containsText" text=" tor" stopIfTrue="1" dxfId="347">
+    <cfRule priority="4" type="containsText" operator="containsText" text=" tor" stopIfTrue="1" dxfId="357">
       <formula>NOT(ISERROR(SEARCH(" tor",A1)))</formula>
     </cfRule>
-    <cfRule priority="5" type="containsText" operator="containsText" text=" proxy" stopIfTrue="1" dxfId="347">
+    <cfRule priority="5" type="containsText" operator="containsText" text=" proxy" stopIfTrue="1" dxfId="357">
       <formula>NOT(ISERROR(SEARCH(" proxy",A1)))</formula>
     </cfRule>
-    <cfRule priority="6" type="containsText" operator="containsText" text=" hosting" stopIfTrue="1" dxfId="348">
+    <cfRule priority="6" type="containsText" operator="containsText" text=" hosting" stopIfTrue="1" dxfId="358">
       <formula>NOT(ISERROR(SEARCH(" hosting",A1)))</formula>
     </cfRule>
-    <cfRule priority="7" type="containsText" operator="containsText" text=" cloud" stopIfTrue="1" dxfId="348">
+    <cfRule priority="7" type="containsText" operator="containsText" text=" cloud" stopIfTrue="1" dxfId="358">
       <formula>NOT(ISERROR(SEARCH(" cloud",A1)))</formula>
     </cfRule>
-    <cfRule priority="8" type="containsText" operator="containsText" text=" datacenter" stopIfTrue="1" dxfId="348">
+    <cfRule priority="8" type="containsText" operator="containsText" text=" datacenter" stopIfTrue="1" dxfId="358">
       <formula>NOT(ISERROR(SEARCH(" datacenter",A1)))</formula>
     </cfRule>
-    <cfRule priority="9" type="containsText" operator="containsText" text="mobile" stopIfTrue="1" dxfId="349">
+    <cfRule priority="9" type="containsText" operator="containsText" text="mobile" stopIfTrue="1" dxfId="359">
       <formula>NOT(ISERROR(SEARCH("mobile",A1)))</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Data/IpAddressConditionalFormattingTemplate.xlsx
+++ b/Data/IpAddressConditionalFormattingTemplate.xlsx
@@ -195,7 +195,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="360">
+  <dxfs count="375">
     <dxf>
       <fill>
         <patternFill>
@@ -262,6 +262,111 @@
     <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ffadd8e6"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ff59abf8"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ffffb6c1"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="fffacd90"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="fff2ceef"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ffadd8e6"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ff59abf8"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ffffb6c1"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="fffacd90"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="fff2ceef"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ffadd8e6"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ff59abf8"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ffffb6c1"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="fffacd90"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="fff2ceef"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
     <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
       <fill>
         <patternFill>
@@ -3209,31 +3314,31 @@
     <row r="78" ht="15" customHeight="1"/>
   </sheetData>
   <conditionalFormatting sqref="A:A">
-    <cfRule priority="1" type="containsText" operator="containsText" text="microsoft" stopIfTrue="1" dxfId="355">
+    <cfRule priority="1" type="containsText" operator="containsText" text="microsoft" stopIfTrue="1" dxfId="370">
       <formula>NOT(ISERROR(SEARCH("microsoft",A1)))</formula>
     </cfRule>
-    <cfRule priority="2" type="containsText" operator="containsText" text="proofpoint" stopIfTrue="1" dxfId="356">
+    <cfRule priority="2" type="containsText" operator="containsText" text="proofpoint" stopIfTrue="1" dxfId="371">
       <formula>NOT(ISERROR(SEARCH("proofpoint",A1)))</formula>
     </cfRule>
-    <cfRule priority="3" type="containsText" operator="containsText" text=" vpn" stopIfTrue="1" dxfId="357">
+    <cfRule priority="3" type="containsText" operator="containsText" text=" vpn" stopIfTrue="1" dxfId="372">
       <formula>NOT(ISERROR(SEARCH(" vpn",A1)))</formula>
     </cfRule>
-    <cfRule priority="4" type="containsText" operator="containsText" text=" tor" stopIfTrue="1" dxfId="357">
+    <cfRule priority="4" type="containsText" operator="containsText" text=" tor" stopIfTrue="1" dxfId="372">
       <formula>NOT(ISERROR(SEARCH(" tor",A1)))</formula>
     </cfRule>
-    <cfRule priority="5" type="containsText" operator="containsText" text=" proxy" stopIfTrue="1" dxfId="357">
+    <cfRule priority="5" type="containsText" operator="containsText" text=" proxy" stopIfTrue="1" dxfId="372">
       <formula>NOT(ISERROR(SEARCH(" proxy",A1)))</formula>
     </cfRule>
-    <cfRule priority="6" type="containsText" operator="containsText" text=" hosting" stopIfTrue="1" dxfId="358">
+    <cfRule priority="6" type="containsText" operator="containsText" text=" hosting" stopIfTrue="1" dxfId="373">
       <formula>NOT(ISERROR(SEARCH(" hosting",A1)))</formula>
     </cfRule>
-    <cfRule priority="7" type="containsText" operator="containsText" text=" cloud" stopIfTrue="1" dxfId="358">
+    <cfRule priority="7" type="containsText" operator="containsText" text=" cloud" stopIfTrue="1" dxfId="373">
       <formula>NOT(ISERROR(SEARCH(" cloud",A1)))</formula>
     </cfRule>
-    <cfRule priority="8" type="containsText" operator="containsText" text=" datacenter" stopIfTrue="1" dxfId="358">
+    <cfRule priority="8" type="containsText" operator="containsText" text=" datacenter" stopIfTrue="1" dxfId="373">
       <formula>NOT(ISERROR(SEARCH(" datacenter",A1)))</formula>
     </cfRule>
-    <cfRule priority="9" type="containsText" operator="containsText" text="mobile" stopIfTrue="1" dxfId="359">
+    <cfRule priority="9" type="containsText" operator="containsText" text="mobile" stopIfTrue="1" dxfId="374">
       <formula>NOT(ISERROR(SEARCH("mobile",A1)))</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Data/IpAddressConditionalFormattingTemplate.xlsx
+++ b/Data/IpAddressConditionalFormattingTemplate.xlsx
@@ -195,7 +195,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="375">
+  <dxfs count="380">
     <dxf>
       <fill>
         <patternFill>
@@ -262,6 +262,41 @@
     <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ffadd8e6"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ff59abf8"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ffffb6c1"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="fffacd90"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="fff2ceef"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
     <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
       <fill>
         <patternFill>
@@ -3314,31 +3349,31 @@
     <row r="78" ht="15" customHeight="1"/>
   </sheetData>
   <conditionalFormatting sqref="A:A">
-    <cfRule priority="1" type="containsText" operator="containsText" text="microsoft" stopIfTrue="1" dxfId="370">
+    <cfRule priority="1" type="containsText" operator="containsText" text="microsoft" stopIfTrue="1" dxfId="375">
       <formula>NOT(ISERROR(SEARCH("microsoft",A1)))</formula>
     </cfRule>
-    <cfRule priority="2" type="containsText" operator="containsText" text="proofpoint" stopIfTrue="1" dxfId="371">
+    <cfRule priority="2" type="containsText" operator="containsText" text="proofpoint" stopIfTrue="1" dxfId="376">
       <formula>NOT(ISERROR(SEARCH("proofpoint",A1)))</formula>
     </cfRule>
-    <cfRule priority="3" type="containsText" operator="containsText" text=" vpn" stopIfTrue="1" dxfId="372">
+    <cfRule priority="3" type="containsText" operator="containsText" text=" vpn" stopIfTrue="1" dxfId="377">
       <formula>NOT(ISERROR(SEARCH(" vpn",A1)))</formula>
     </cfRule>
-    <cfRule priority="4" type="containsText" operator="containsText" text=" tor" stopIfTrue="1" dxfId="372">
+    <cfRule priority="4" type="containsText" operator="containsText" text=" tor" stopIfTrue="1" dxfId="377">
       <formula>NOT(ISERROR(SEARCH(" tor",A1)))</formula>
     </cfRule>
-    <cfRule priority="5" type="containsText" operator="containsText" text=" proxy" stopIfTrue="1" dxfId="372">
+    <cfRule priority="5" type="containsText" operator="containsText" text=" proxy" stopIfTrue="1" dxfId="377">
       <formula>NOT(ISERROR(SEARCH(" proxy",A1)))</formula>
     </cfRule>
-    <cfRule priority="6" type="containsText" operator="containsText" text=" hosting" stopIfTrue="1" dxfId="373">
+    <cfRule priority="6" type="containsText" operator="containsText" text=" hosting" stopIfTrue="1" dxfId="378">
       <formula>NOT(ISERROR(SEARCH(" hosting",A1)))</formula>
     </cfRule>
-    <cfRule priority="7" type="containsText" operator="containsText" text=" cloud" stopIfTrue="1" dxfId="373">
+    <cfRule priority="7" type="containsText" operator="containsText" text=" cloud" stopIfTrue="1" dxfId="378">
       <formula>NOT(ISERROR(SEARCH(" cloud",A1)))</formula>
     </cfRule>
-    <cfRule priority="8" type="containsText" operator="containsText" text=" datacenter" stopIfTrue="1" dxfId="373">
+    <cfRule priority="8" type="containsText" operator="containsText" text=" datacenter" stopIfTrue="1" dxfId="378">
       <formula>NOT(ISERROR(SEARCH(" datacenter",A1)))</formula>
     </cfRule>
-    <cfRule priority="9" type="containsText" operator="containsText" text="mobile" stopIfTrue="1" dxfId="374">
+    <cfRule priority="9" type="containsText" operator="containsText" text="mobile" stopIfTrue="1" dxfId="379">
       <formula>NOT(ISERROR(SEARCH("mobile",A1)))</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Data/IpAddressConditionalFormattingTemplate.xlsx
+++ b/Data/IpAddressConditionalFormattingTemplate.xlsx
@@ -195,7 +195,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="380">
+  <dxfs count="385">
     <dxf>
       <fill>
         <patternFill>
@@ -262,6 +262,41 @@
     <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ffadd8e6"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ff59abf8"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ffffb6c1"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="fffacd90"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="fff2ceef"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
     <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
       <fill>
         <patternFill>
@@ -3349,31 +3384,31 @@
     <row r="78" ht="15" customHeight="1"/>
   </sheetData>
   <conditionalFormatting sqref="A:A">
-    <cfRule priority="1" type="containsText" operator="containsText" text="microsoft" stopIfTrue="1" dxfId="375">
+    <cfRule priority="1" type="containsText" operator="containsText" text="microsoft" stopIfTrue="1" dxfId="380">
       <formula>NOT(ISERROR(SEARCH("microsoft",A1)))</formula>
     </cfRule>
-    <cfRule priority="2" type="containsText" operator="containsText" text="proofpoint" stopIfTrue="1" dxfId="376">
+    <cfRule priority="2" type="containsText" operator="containsText" text="proofpoint" stopIfTrue="1" dxfId="381">
       <formula>NOT(ISERROR(SEARCH("proofpoint",A1)))</formula>
     </cfRule>
-    <cfRule priority="3" type="containsText" operator="containsText" text=" vpn" stopIfTrue="1" dxfId="377">
+    <cfRule priority="3" type="containsText" operator="containsText" text=" vpn" stopIfTrue="1" dxfId="382">
       <formula>NOT(ISERROR(SEARCH(" vpn",A1)))</formula>
     </cfRule>
-    <cfRule priority="4" type="containsText" operator="containsText" text=" tor" stopIfTrue="1" dxfId="377">
+    <cfRule priority="4" type="containsText" operator="containsText" text=" tor" stopIfTrue="1" dxfId="382">
       <formula>NOT(ISERROR(SEARCH(" tor",A1)))</formula>
     </cfRule>
-    <cfRule priority="5" type="containsText" operator="containsText" text=" proxy" stopIfTrue="1" dxfId="377">
+    <cfRule priority="5" type="containsText" operator="containsText" text=" proxy" stopIfTrue="1" dxfId="382">
       <formula>NOT(ISERROR(SEARCH(" proxy",A1)))</formula>
     </cfRule>
-    <cfRule priority="6" type="containsText" operator="containsText" text=" hosting" stopIfTrue="1" dxfId="378">
+    <cfRule priority="6" type="containsText" operator="containsText" text=" hosting" stopIfTrue="1" dxfId="383">
       <formula>NOT(ISERROR(SEARCH(" hosting",A1)))</formula>
     </cfRule>
-    <cfRule priority="7" type="containsText" operator="containsText" text=" cloud" stopIfTrue="1" dxfId="378">
+    <cfRule priority="7" type="containsText" operator="containsText" text=" cloud" stopIfTrue="1" dxfId="383">
       <formula>NOT(ISERROR(SEARCH(" cloud",A1)))</formula>
     </cfRule>
-    <cfRule priority="8" type="containsText" operator="containsText" text=" datacenter" stopIfTrue="1" dxfId="378">
+    <cfRule priority="8" type="containsText" operator="containsText" text=" datacenter" stopIfTrue="1" dxfId="383">
       <formula>NOT(ISERROR(SEARCH(" datacenter",A1)))</formula>
     </cfRule>
-    <cfRule priority="9" type="containsText" operator="containsText" text="mobile" stopIfTrue="1" dxfId="379">
+    <cfRule priority="9" type="containsText" operator="containsText" text="mobile" stopIfTrue="1" dxfId="384">
       <formula>NOT(ISERROR(SEARCH("mobile",A1)))</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Data/IpAddressConditionalFormattingTemplate.xlsx
+++ b/Data/IpAddressConditionalFormattingTemplate.xlsx
@@ -195,7 +195,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="385">
+  <dxfs count="410">
     <dxf>
       <fill>
         <patternFill>
@@ -262,6 +262,181 @@
     <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ffadd8e6"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ff59abf8"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ffffb6c1"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="fffacd90"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="fff2ceef"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ffadd8e6"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ff59abf8"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ffffb6c1"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="fffacd90"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="fff2ceef"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ffadd8e6"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ff59abf8"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ffffb6c1"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="fffacd90"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="fff2ceef"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ffadd8e6"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ff59abf8"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ffffb6c1"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="fffacd90"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="fff2ceef"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ffadd8e6"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ff59abf8"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ffffb6c1"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="fffacd90"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="fff2ceef"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
     <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
       <fill>
         <patternFill>
@@ -3384,31 +3559,31 @@
     <row r="78" ht="15" customHeight="1"/>
   </sheetData>
   <conditionalFormatting sqref="A:A">
-    <cfRule priority="1" type="containsText" operator="containsText" text="microsoft" stopIfTrue="1" dxfId="380">
+    <cfRule priority="1" type="containsText" operator="containsText" text="microsoft" stopIfTrue="1" dxfId="405">
       <formula>NOT(ISERROR(SEARCH("microsoft",A1)))</formula>
     </cfRule>
-    <cfRule priority="2" type="containsText" operator="containsText" text="proofpoint" stopIfTrue="1" dxfId="381">
+    <cfRule priority="2" type="containsText" operator="containsText" text="proofpoint" stopIfTrue="1" dxfId="406">
       <formula>NOT(ISERROR(SEARCH("proofpoint",A1)))</formula>
     </cfRule>
-    <cfRule priority="3" type="containsText" operator="containsText" text=" vpn" stopIfTrue="1" dxfId="382">
+    <cfRule priority="3" type="containsText" operator="containsText" text=" vpn" stopIfTrue="1" dxfId="407">
       <formula>NOT(ISERROR(SEARCH(" vpn",A1)))</formula>
     </cfRule>
-    <cfRule priority="4" type="containsText" operator="containsText" text=" tor" stopIfTrue="1" dxfId="382">
+    <cfRule priority="4" type="containsText" operator="containsText" text=" tor" stopIfTrue="1" dxfId="407">
       <formula>NOT(ISERROR(SEARCH(" tor",A1)))</formula>
     </cfRule>
-    <cfRule priority="5" type="containsText" operator="containsText" text=" proxy" stopIfTrue="1" dxfId="382">
+    <cfRule priority="5" type="containsText" operator="containsText" text=" proxy" stopIfTrue="1" dxfId="407">
       <formula>NOT(ISERROR(SEARCH(" proxy",A1)))</formula>
     </cfRule>
-    <cfRule priority="6" type="containsText" operator="containsText" text=" hosting" stopIfTrue="1" dxfId="383">
+    <cfRule priority="6" type="containsText" operator="containsText" text=" hosting" stopIfTrue="1" dxfId="408">
       <formula>NOT(ISERROR(SEARCH(" hosting",A1)))</formula>
     </cfRule>
-    <cfRule priority="7" type="containsText" operator="containsText" text=" cloud" stopIfTrue="1" dxfId="383">
+    <cfRule priority="7" type="containsText" operator="containsText" text=" cloud" stopIfTrue="1" dxfId="408">
       <formula>NOT(ISERROR(SEARCH(" cloud",A1)))</formula>
     </cfRule>
-    <cfRule priority="8" type="containsText" operator="containsText" text=" datacenter" stopIfTrue="1" dxfId="383">
+    <cfRule priority="8" type="containsText" operator="containsText" text=" datacenter" stopIfTrue="1" dxfId="408">
       <formula>NOT(ISERROR(SEARCH(" datacenter",A1)))</formula>
     </cfRule>
-    <cfRule priority="9" type="containsText" operator="containsText" text="mobile" stopIfTrue="1" dxfId="384">
+    <cfRule priority="9" type="containsText" operator="containsText" text="mobile" stopIfTrue="1" dxfId="409">
       <formula>NOT(ISERROR(SEARCH("mobile",A1)))</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Data/IpAddressConditionalFormattingTemplate.xlsx
+++ b/Data/IpAddressConditionalFormattingTemplate.xlsx
@@ -195,7 +195,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="410">
+  <dxfs count="420">
     <dxf>
       <fill>
         <patternFill>
@@ -262,6 +262,76 @@
     <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ffadd8e6"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ff59abf8"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ffffb6c1"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="fffacd90"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="fff2ceef"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ffadd8e6"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ff59abf8"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ffffb6c1"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="fffacd90"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="fff2ceef"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
     <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
       <fill>
         <patternFill>
@@ -3559,31 +3629,31 @@
     <row r="78" ht="15" customHeight="1"/>
   </sheetData>
   <conditionalFormatting sqref="A:A">
-    <cfRule priority="1" type="containsText" operator="containsText" text="microsoft" stopIfTrue="1" dxfId="405">
+    <cfRule priority="1" type="containsText" operator="containsText" text="microsoft" stopIfTrue="1" dxfId="415">
       <formula>NOT(ISERROR(SEARCH("microsoft",A1)))</formula>
     </cfRule>
-    <cfRule priority="2" type="containsText" operator="containsText" text="proofpoint" stopIfTrue="1" dxfId="406">
+    <cfRule priority="2" type="containsText" operator="containsText" text="proofpoint" stopIfTrue="1" dxfId="416">
       <formula>NOT(ISERROR(SEARCH("proofpoint",A1)))</formula>
     </cfRule>
-    <cfRule priority="3" type="containsText" operator="containsText" text=" vpn" stopIfTrue="1" dxfId="407">
+    <cfRule priority="3" type="containsText" operator="containsText" text=" vpn" stopIfTrue="1" dxfId="417">
       <formula>NOT(ISERROR(SEARCH(" vpn",A1)))</formula>
     </cfRule>
-    <cfRule priority="4" type="containsText" operator="containsText" text=" tor" stopIfTrue="1" dxfId="407">
+    <cfRule priority="4" type="containsText" operator="containsText" text=" tor" stopIfTrue="1" dxfId="417">
       <formula>NOT(ISERROR(SEARCH(" tor",A1)))</formula>
     </cfRule>
-    <cfRule priority="5" type="containsText" operator="containsText" text=" proxy" stopIfTrue="1" dxfId="407">
+    <cfRule priority="5" type="containsText" operator="containsText" text=" proxy" stopIfTrue="1" dxfId="417">
       <formula>NOT(ISERROR(SEARCH(" proxy",A1)))</formula>
     </cfRule>
-    <cfRule priority="6" type="containsText" operator="containsText" text=" hosting" stopIfTrue="1" dxfId="408">
+    <cfRule priority="6" type="containsText" operator="containsText" text=" hosting" stopIfTrue="1" dxfId="418">
       <formula>NOT(ISERROR(SEARCH(" hosting",A1)))</formula>
     </cfRule>
-    <cfRule priority="7" type="containsText" operator="containsText" text=" cloud" stopIfTrue="1" dxfId="408">
+    <cfRule priority="7" type="containsText" operator="containsText" text=" cloud" stopIfTrue="1" dxfId="418">
       <formula>NOT(ISERROR(SEARCH(" cloud",A1)))</formula>
     </cfRule>
-    <cfRule priority="8" type="containsText" operator="containsText" text=" datacenter" stopIfTrue="1" dxfId="408">
+    <cfRule priority="8" type="containsText" operator="containsText" text=" datacenter" stopIfTrue="1" dxfId="418">
       <formula>NOT(ISERROR(SEARCH(" datacenter",A1)))</formula>
     </cfRule>
-    <cfRule priority="9" type="containsText" operator="containsText" text="mobile" stopIfTrue="1" dxfId="409">
+    <cfRule priority="9" type="containsText" operator="containsText" text="mobile" stopIfTrue="1" dxfId="419">
       <formula>NOT(ISERROR(SEARCH("mobile",A1)))</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Data/IpAddressConditionalFormattingTemplate.xlsx
+++ b/Data/IpAddressConditionalFormattingTemplate.xlsx
@@ -195,7 +195,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="420">
+  <dxfs count="430">
     <dxf>
       <fill>
         <patternFill>
@@ -262,6 +262,76 @@
     <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ffadd8e6"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ff59abf8"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ffffb6c1"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="fffacd90"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="fff2ceef"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ffadd8e6"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ff59abf8"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ffffb6c1"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="fffacd90"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="fff2ceef"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
     <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
       <fill>
         <patternFill>
@@ -3629,31 +3699,31 @@
     <row r="78" ht="15" customHeight="1"/>
   </sheetData>
   <conditionalFormatting sqref="A:A">
-    <cfRule priority="1" type="containsText" operator="containsText" text="microsoft" stopIfTrue="1" dxfId="415">
+    <cfRule priority="1" type="containsText" operator="containsText" text="microsoft" stopIfTrue="1" dxfId="425">
       <formula>NOT(ISERROR(SEARCH("microsoft",A1)))</formula>
     </cfRule>
-    <cfRule priority="2" type="containsText" operator="containsText" text="proofpoint" stopIfTrue="1" dxfId="416">
+    <cfRule priority="2" type="containsText" operator="containsText" text="proofpoint" stopIfTrue="1" dxfId="426">
       <formula>NOT(ISERROR(SEARCH("proofpoint",A1)))</formula>
     </cfRule>
-    <cfRule priority="3" type="containsText" operator="containsText" text=" vpn" stopIfTrue="1" dxfId="417">
+    <cfRule priority="3" type="containsText" operator="containsText" text=" vpn" stopIfTrue="1" dxfId="427">
       <formula>NOT(ISERROR(SEARCH(" vpn",A1)))</formula>
     </cfRule>
-    <cfRule priority="4" type="containsText" operator="containsText" text=" tor" stopIfTrue="1" dxfId="417">
+    <cfRule priority="4" type="containsText" operator="containsText" text=" tor" stopIfTrue="1" dxfId="427">
       <formula>NOT(ISERROR(SEARCH(" tor",A1)))</formula>
     </cfRule>
-    <cfRule priority="5" type="containsText" operator="containsText" text=" proxy" stopIfTrue="1" dxfId="417">
+    <cfRule priority="5" type="containsText" operator="containsText" text=" proxy" stopIfTrue="1" dxfId="427">
       <formula>NOT(ISERROR(SEARCH(" proxy",A1)))</formula>
     </cfRule>
-    <cfRule priority="6" type="containsText" operator="containsText" text=" hosting" stopIfTrue="1" dxfId="418">
+    <cfRule priority="6" type="containsText" operator="containsText" text=" hosting" stopIfTrue="1" dxfId="428">
       <formula>NOT(ISERROR(SEARCH(" hosting",A1)))</formula>
     </cfRule>
-    <cfRule priority="7" type="containsText" operator="containsText" text=" cloud" stopIfTrue="1" dxfId="418">
+    <cfRule priority="7" type="containsText" operator="containsText" text=" cloud" stopIfTrue="1" dxfId="428">
       <formula>NOT(ISERROR(SEARCH(" cloud",A1)))</formula>
     </cfRule>
-    <cfRule priority="8" type="containsText" operator="containsText" text=" datacenter" stopIfTrue="1" dxfId="418">
+    <cfRule priority="8" type="containsText" operator="containsText" text=" datacenter" stopIfTrue="1" dxfId="428">
       <formula>NOT(ISERROR(SEARCH(" datacenter",A1)))</formula>
     </cfRule>
-    <cfRule priority="9" type="containsText" operator="containsText" text="mobile" stopIfTrue="1" dxfId="419">
+    <cfRule priority="9" type="containsText" operator="containsText" text="mobile" stopIfTrue="1" dxfId="429">
       <formula>NOT(ISERROR(SEARCH("mobile",A1)))</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Data/IpAddressConditionalFormattingTemplate.xlsx
+++ b/Data/IpAddressConditionalFormattingTemplate.xlsx
@@ -195,7 +195,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="430">
+  <dxfs count="435">
     <dxf>
       <fill>
         <patternFill>
@@ -262,6 +262,41 @@
     <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ffadd8e6"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ff59abf8"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ffffb6c1"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="fffacd90"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="fff2ceef"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
     <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
       <fill>
         <patternFill>
@@ -3699,31 +3734,31 @@
     <row r="78" ht="15" customHeight="1"/>
   </sheetData>
   <conditionalFormatting sqref="A:A">
-    <cfRule priority="1" type="containsText" operator="containsText" text="microsoft" stopIfTrue="1" dxfId="425">
+    <cfRule priority="1" type="containsText" operator="containsText" text="microsoft" stopIfTrue="1" dxfId="430">
       <formula>NOT(ISERROR(SEARCH("microsoft",A1)))</formula>
     </cfRule>
-    <cfRule priority="2" type="containsText" operator="containsText" text="proofpoint" stopIfTrue="1" dxfId="426">
+    <cfRule priority="2" type="containsText" operator="containsText" text="proofpoint" stopIfTrue="1" dxfId="431">
       <formula>NOT(ISERROR(SEARCH("proofpoint",A1)))</formula>
     </cfRule>
-    <cfRule priority="3" type="containsText" operator="containsText" text=" vpn" stopIfTrue="1" dxfId="427">
+    <cfRule priority="3" type="containsText" operator="containsText" text=" vpn" stopIfTrue="1" dxfId="432">
       <formula>NOT(ISERROR(SEARCH(" vpn",A1)))</formula>
     </cfRule>
-    <cfRule priority="4" type="containsText" operator="containsText" text=" tor" stopIfTrue="1" dxfId="427">
+    <cfRule priority="4" type="containsText" operator="containsText" text=" tor" stopIfTrue="1" dxfId="432">
       <formula>NOT(ISERROR(SEARCH(" tor",A1)))</formula>
     </cfRule>
-    <cfRule priority="5" type="containsText" operator="containsText" text=" proxy" stopIfTrue="1" dxfId="427">
+    <cfRule priority="5" type="containsText" operator="containsText" text=" proxy" stopIfTrue="1" dxfId="432">
       <formula>NOT(ISERROR(SEARCH(" proxy",A1)))</formula>
     </cfRule>
-    <cfRule priority="6" type="containsText" operator="containsText" text=" hosting" stopIfTrue="1" dxfId="428">
+    <cfRule priority="6" type="containsText" operator="containsText" text=" hosting" stopIfTrue="1" dxfId="433">
       <formula>NOT(ISERROR(SEARCH(" hosting",A1)))</formula>
     </cfRule>
-    <cfRule priority="7" type="containsText" operator="containsText" text=" cloud" stopIfTrue="1" dxfId="428">
+    <cfRule priority="7" type="containsText" operator="containsText" text=" cloud" stopIfTrue="1" dxfId="433">
       <formula>NOT(ISERROR(SEARCH(" cloud",A1)))</formula>
     </cfRule>
-    <cfRule priority="8" type="containsText" operator="containsText" text=" datacenter" stopIfTrue="1" dxfId="428">
+    <cfRule priority="8" type="containsText" operator="containsText" text=" datacenter" stopIfTrue="1" dxfId="433">
       <formula>NOT(ISERROR(SEARCH(" datacenter",A1)))</formula>
     </cfRule>
-    <cfRule priority="9" type="containsText" operator="containsText" text="mobile" stopIfTrue="1" dxfId="429">
+    <cfRule priority="9" type="containsText" operator="containsText" text="mobile" stopIfTrue="1" dxfId="434">
       <formula>NOT(ISERROR(SEARCH("mobile",A1)))</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Data/IpAddressConditionalFormattingTemplate.xlsx
+++ b/Data/IpAddressConditionalFormattingTemplate.xlsx
@@ -195,7 +195,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="435">
+  <dxfs count="440">
     <dxf>
       <fill>
         <patternFill>
@@ -262,6 +262,41 @@
     <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ffadd8e6"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ff59abf8"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ffffb6c1"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="fffacd90"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="fff2ceef"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
     <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
       <fill>
         <patternFill>
@@ -3734,31 +3769,31 @@
     <row r="78" ht="15" customHeight="1"/>
   </sheetData>
   <conditionalFormatting sqref="A:A">
-    <cfRule priority="1" type="containsText" operator="containsText" text="microsoft" stopIfTrue="1" dxfId="430">
+    <cfRule priority="1" type="containsText" operator="containsText" text="microsoft" stopIfTrue="1" dxfId="435">
       <formula>NOT(ISERROR(SEARCH("microsoft",A1)))</formula>
     </cfRule>
-    <cfRule priority="2" type="containsText" operator="containsText" text="proofpoint" stopIfTrue="1" dxfId="431">
+    <cfRule priority="2" type="containsText" operator="containsText" text="proofpoint" stopIfTrue="1" dxfId="436">
       <formula>NOT(ISERROR(SEARCH("proofpoint",A1)))</formula>
     </cfRule>
-    <cfRule priority="3" type="containsText" operator="containsText" text=" vpn" stopIfTrue="1" dxfId="432">
+    <cfRule priority="3" type="containsText" operator="containsText" text=" vpn" stopIfTrue="1" dxfId="437">
       <formula>NOT(ISERROR(SEARCH(" vpn",A1)))</formula>
     </cfRule>
-    <cfRule priority="4" type="containsText" operator="containsText" text=" tor" stopIfTrue="1" dxfId="432">
+    <cfRule priority="4" type="containsText" operator="containsText" text=" tor" stopIfTrue="1" dxfId="437">
       <formula>NOT(ISERROR(SEARCH(" tor",A1)))</formula>
     </cfRule>
-    <cfRule priority="5" type="containsText" operator="containsText" text=" proxy" stopIfTrue="1" dxfId="432">
+    <cfRule priority="5" type="containsText" operator="containsText" text=" proxy" stopIfTrue="1" dxfId="437">
       <formula>NOT(ISERROR(SEARCH(" proxy",A1)))</formula>
     </cfRule>
-    <cfRule priority="6" type="containsText" operator="containsText" text=" hosting" stopIfTrue="1" dxfId="433">
+    <cfRule priority="6" type="containsText" operator="containsText" text=" hosting" stopIfTrue="1" dxfId="438">
       <formula>NOT(ISERROR(SEARCH(" hosting",A1)))</formula>
     </cfRule>
-    <cfRule priority="7" type="containsText" operator="containsText" text=" cloud" stopIfTrue="1" dxfId="433">
+    <cfRule priority="7" type="containsText" operator="containsText" text=" cloud" stopIfTrue="1" dxfId="438">
       <formula>NOT(ISERROR(SEARCH(" cloud",A1)))</formula>
     </cfRule>
-    <cfRule priority="8" type="containsText" operator="containsText" text=" datacenter" stopIfTrue="1" dxfId="433">
+    <cfRule priority="8" type="containsText" operator="containsText" text=" datacenter" stopIfTrue="1" dxfId="438">
       <formula>NOT(ISERROR(SEARCH(" datacenter",A1)))</formula>
     </cfRule>
-    <cfRule priority="9" type="containsText" operator="containsText" text="mobile" stopIfTrue="1" dxfId="434">
+    <cfRule priority="9" type="containsText" operator="containsText" text="mobile" stopIfTrue="1" dxfId="439">
       <formula>NOT(ISERROR(SEARCH("mobile",A1)))</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Data/IpAddressConditionalFormattingTemplate.xlsx
+++ b/Data/IpAddressConditionalFormattingTemplate.xlsx
@@ -195,7 +195,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="440">
+  <dxfs count="455">
     <dxf>
       <fill>
         <patternFill>
@@ -262,6 +262,111 @@
     <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ffadd8e6"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ff59abf8"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ffffb6c1"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="fffacd90"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="fff2ceef"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ffadd8e6"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ff59abf8"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ffffb6c1"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="fffacd90"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="fff2ceef"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ffadd8e6"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ff59abf8"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ffffb6c1"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="fffacd90"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="fff2ceef"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
     <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
       <fill>
         <patternFill>
@@ -3769,31 +3874,31 @@
     <row r="78" ht="15" customHeight="1"/>
   </sheetData>
   <conditionalFormatting sqref="A:A">
-    <cfRule priority="1" type="containsText" operator="containsText" text="microsoft" stopIfTrue="1" dxfId="435">
+    <cfRule priority="1" type="containsText" operator="containsText" text="microsoft" stopIfTrue="1" dxfId="450">
       <formula>NOT(ISERROR(SEARCH("microsoft",A1)))</formula>
     </cfRule>
-    <cfRule priority="2" type="containsText" operator="containsText" text="proofpoint" stopIfTrue="1" dxfId="436">
+    <cfRule priority="2" type="containsText" operator="containsText" text="proofpoint" stopIfTrue="1" dxfId="451">
       <formula>NOT(ISERROR(SEARCH("proofpoint",A1)))</formula>
     </cfRule>
-    <cfRule priority="3" type="containsText" operator="containsText" text=" vpn" stopIfTrue="1" dxfId="437">
+    <cfRule priority="3" type="containsText" operator="containsText" text=" vpn" stopIfTrue="1" dxfId="452">
       <formula>NOT(ISERROR(SEARCH(" vpn",A1)))</formula>
     </cfRule>
-    <cfRule priority="4" type="containsText" operator="containsText" text=" tor" stopIfTrue="1" dxfId="437">
+    <cfRule priority="4" type="containsText" operator="containsText" text=" tor" stopIfTrue="1" dxfId="452">
       <formula>NOT(ISERROR(SEARCH(" tor",A1)))</formula>
     </cfRule>
-    <cfRule priority="5" type="containsText" operator="containsText" text=" proxy" stopIfTrue="1" dxfId="437">
+    <cfRule priority="5" type="containsText" operator="containsText" text=" proxy" stopIfTrue="1" dxfId="452">
       <formula>NOT(ISERROR(SEARCH(" proxy",A1)))</formula>
     </cfRule>
-    <cfRule priority="6" type="containsText" operator="containsText" text=" hosting" stopIfTrue="1" dxfId="438">
+    <cfRule priority="6" type="containsText" operator="containsText" text=" hosting" stopIfTrue="1" dxfId="453">
       <formula>NOT(ISERROR(SEARCH(" hosting",A1)))</formula>
     </cfRule>
-    <cfRule priority="7" type="containsText" operator="containsText" text=" cloud" stopIfTrue="1" dxfId="438">
+    <cfRule priority="7" type="containsText" operator="containsText" text=" cloud" stopIfTrue="1" dxfId="453">
       <formula>NOT(ISERROR(SEARCH(" cloud",A1)))</formula>
     </cfRule>
-    <cfRule priority="8" type="containsText" operator="containsText" text=" datacenter" stopIfTrue="1" dxfId="438">
+    <cfRule priority="8" type="containsText" operator="containsText" text=" datacenter" stopIfTrue="1" dxfId="453">
       <formula>NOT(ISERROR(SEARCH(" datacenter",A1)))</formula>
     </cfRule>
-    <cfRule priority="9" type="containsText" operator="containsText" text="mobile" stopIfTrue="1" dxfId="439">
+    <cfRule priority="9" type="containsText" operator="containsText" text="mobile" stopIfTrue="1" dxfId="454">
       <formula>NOT(ISERROR(SEARCH("mobile",A1)))</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Data/IpAddressConditionalFormattingTemplate.xlsx
+++ b/Data/IpAddressConditionalFormattingTemplate.xlsx
@@ -195,7 +195,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="455">
+  <dxfs count="460">
     <dxf>
       <fill>
         <patternFill>
@@ -262,6 +262,41 @@
     <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ffadd8e6"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ff59abf8"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ffffb6c1"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="fffacd90"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="fff2ceef"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
     <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
       <fill>
         <patternFill>
@@ -3874,31 +3909,31 @@
     <row r="78" ht="15" customHeight="1"/>
   </sheetData>
   <conditionalFormatting sqref="A:A">
-    <cfRule priority="1" type="containsText" operator="containsText" text="microsoft" stopIfTrue="1" dxfId="450">
+    <cfRule priority="1" type="containsText" operator="containsText" text="microsoft" stopIfTrue="1" dxfId="455">
       <formula>NOT(ISERROR(SEARCH("microsoft",A1)))</formula>
     </cfRule>
-    <cfRule priority="2" type="containsText" operator="containsText" text="proofpoint" stopIfTrue="1" dxfId="451">
+    <cfRule priority="2" type="containsText" operator="containsText" text="proofpoint" stopIfTrue="1" dxfId="456">
       <formula>NOT(ISERROR(SEARCH("proofpoint",A1)))</formula>
     </cfRule>
-    <cfRule priority="3" type="containsText" operator="containsText" text=" vpn" stopIfTrue="1" dxfId="452">
+    <cfRule priority="3" type="containsText" operator="containsText" text=" vpn" stopIfTrue="1" dxfId="457">
       <formula>NOT(ISERROR(SEARCH(" vpn",A1)))</formula>
     </cfRule>
-    <cfRule priority="4" type="containsText" operator="containsText" text=" tor" stopIfTrue="1" dxfId="452">
+    <cfRule priority="4" type="containsText" operator="containsText" text=" tor" stopIfTrue="1" dxfId="457">
       <formula>NOT(ISERROR(SEARCH(" tor",A1)))</formula>
     </cfRule>
-    <cfRule priority="5" type="containsText" operator="containsText" text=" proxy" stopIfTrue="1" dxfId="452">
+    <cfRule priority="5" type="containsText" operator="containsText" text=" proxy" stopIfTrue="1" dxfId="457">
       <formula>NOT(ISERROR(SEARCH(" proxy",A1)))</formula>
     </cfRule>
-    <cfRule priority="6" type="containsText" operator="containsText" text=" hosting" stopIfTrue="1" dxfId="453">
+    <cfRule priority="6" type="containsText" operator="containsText" text=" hosting" stopIfTrue="1" dxfId="458">
       <formula>NOT(ISERROR(SEARCH(" hosting",A1)))</formula>
     </cfRule>
-    <cfRule priority="7" type="containsText" operator="containsText" text=" cloud" stopIfTrue="1" dxfId="453">
+    <cfRule priority="7" type="containsText" operator="containsText" text=" cloud" stopIfTrue="1" dxfId="458">
       <formula>NOT(ISERROR(SEARCH(" cloud",A1)))</formula>
     </cfRule>
-    <cfRule priority="8" type="containsText" operator="containsText" text=" datacenter" stopIfTrue="1" dxfId="453">
+    <cfRule priority="8" type="containsText" operator="containsText" text=" datacenter" stopIfTrue="1" dxfId="458">
       <formula>NOT(ISERROR(SEARCH(" datacenter",A1)))</formula>
     </cfRule>
-    <cfRule priority="9" type="containsText" operator="containsText" text="mobile" stopIfTrue="1" dxfId="454">
+    <cfRule priority="9" type="containsText" operator="containsText" text="mobile" stopIfTrue="1" dxfId="459">
       <formula>NOT(ISERROR(SEARCH("mobile",A1)))</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Data/IpAddressConditionalFormattingTemplate.xlsx
+++ b/Data/IpAddressConditionalFormattingTemplate.xlsx
@@ -195,7 +195,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="455">
+  <dxfs count="465">
     <dxf>
       <fill>
         <patternFill>
@@ -262,6 +262,76 @@
     <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ffadd8e6"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ff59abf8"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ffffb6c1"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="fffacd90"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="fff2ceef"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ffadd8e6"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ff59abf8"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="ffffb6c1"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="fffacd90"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
+    <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+      <fill>
+        <patternFill>
+          <bgColor rgb="fff2ceef"/>
+        </patternFill>
+      </fill>
+    </d:dxf>
     <d:dxf xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
       <fill>
         <patternFill>
@@ -3874,31 +3944,31 @@
     <row r="78" ht="15" customHeight="1"/>
   </sheetData>
   <conditionalFormatting sqref="A:A">
-    <cfRule priority="1" type="containsText" operator="containsText" text="microsoft" stopIfTrue="1" dxfId="450">
+    <cfRule priority="1" type="containsText" operator="containsText" text="microsoft" stopIfTrue="1" dxfId="460">
       <formula>NOT(ISERROR(SEARCH("microsoft",A1)))</formula>
     </cfRule>
-    <cfRule priority="2" type="containsText" operator="containsText" text="proofpoint" stopIfTrue="1" dxfId="451">
+    <cfRule priority="2" type="containsText" operator="containsText" text="proofpoint" stopIfTrue="1" dxfId="461">
       <formula>NOT(ISERROR(SEARCH("proofpoint",A1)))</formula>
     </cfRule>
-    <cfRule priority="3" type="containsText" operator="containsText" text=" vpn" stopIfTrue="1" dxfId="452">
+    <cfRule priority="3" type="containsText" operator="containsText" text=" vpn" stopIfTrue="1" dxfId="462">
       <formula>NOT(ISERROR(SEARCH(" vpn",A1)))</formula>
     </cfRule>
-    <cfRule priority="4" type="containsText" operator="containsText" text=" tor" stopIfTrue="1" dxfId="452">
+    <cfRule priority="4" type="containsText" operator="containsText" text=" tor" stopIfTrue="1" dxfId="462">
       <formula>NOT(ISERROR(SEARCH(" tor",A1)))</formula>
     </cfRule>
-    <cfRule priority="5" type="containsText" operator="containsText" text=" proxy" stopIfTrue="1" dxfId="452">
+    <cfRule priority="5" type="containsText" operator="containsText" text=" proxy" stopIfTrue="1" dxfId="462">
       <formula>NOT(ISERROR(SEARCH(" proxy",A1)))</formula>
     </cfRule>
-    <cfRule priority="6" type="containsText" operator="containsText" text=" hosting" stopIfTrue="1" dxfId="453">
+    <cfRule priority="6" type="containsText" operator="containsText" text=" hosting" stopIfTrue="1" dxfId="463">
       <formula>NOT(ISERROR(SEARCH(" hosting",A1)))</formula>
     </cfRule>
-    <cfRule priority="7" type="containsText" operator="containsText" text=" cloud" stopIfTrue="1" dxfId="453">
+    <cfRule priority="7" type="containsText" operator="containsText" text=" cloud" stopIfTrue="1" dxfId="463">
       <formula>NOT(ISERROR(SEARCH(" cloud",A1)))</formula>
     </cfRule>
-    <cfRule priority="8" type="containsText" operator="containsText" text=" datacenter" stopIfTrue="1" dxfId="453">
+    <cfRule priority="8" type="containsText" operator="containsText" text=" datacenter" stopIfTrue="1" dxfId="463">
       <formula>NOT(ISERROR(SEARCH(" datacenter",A1)))</formula>
     </cfRule>
-    <cfRule priority="9" type="containsText" operator="containsText" text="mobile" stopIfTrue="1" dxfId="454">
+    <cfRule priority="9" type="containsText" operator="containsText" text="mobile" stopIfTrue="1" dxfId="464">
       <formula>NOT(ISERROR(SEARCH("mobile",A1)))</formula>
     </cfRule>
   </conditionalFormatting>
